--- a/src/outputs/ss-end-sem-ta_schedule-final.xlsx
+++ b/src/outputs/ss-end-sem-ta_schedule-final.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="268">
   <si>
     <t>Room</t>
   </si>
@@ -47,757 +47,751 @@
     <t>206</t>
   </si>
   <si>
+    <t>Erica Winnie Gado</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Husseini Nimatu</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Nana Adu</t>
+  </si>
+  <si>
+    <t>PB001</t>
+  </si>
+  <si>
+    <t>Kwabena Amankwah Agyemang</t>
+  </si>
+  <si>
+    <t>PB008</t>
+  </si>
+  <si>
+    <t>Ivy Kuukua Sika Bentil</t>
+  </si>
+  <si>
+    <t>PB014</t>
+  </si>
+  <si>
+    <t>Perfect Mawuli Keti</t>
+  </si>
+  <si>
+    <t>PB020</t>
+  </si>
+  <si>
+    <t>Jesse Turkson</t>
+  </si>
+  <si>
+    <t>PB201</t>
+  </si>
+  <si>
+    <t>Lawson Komla Adobor</t>
+  </si>
+  <si>
+    <t>PB208</t>
+  </si>
+  <si>
+    <t>Eric Mensah</t>
+  </si>
+  <si>
+    <t>PB212</t>
+  </si>
+  <si>
+    <t>George Wiafe</t>
+  </si>
+  <si>
+    <t>PB214</t>
+  </si>
+  <si>
+    <t>Josephine Aduku</t>
+  </si>
+  <si>
+    <t>A110</t>
+  </si>
+  <si>
+    <t>Abdulai Fatimah</t>
+  </si>
+  <si>
+    <t>NAF1</t>
+  </si>
+  <si>
+    <t>Christian Kofi Essandoh / Kadzi Daniel</t>
+  </si>
+  <si>
+    <t>NEB-FF1</t>
+  </si>
+  <si>
+    <t>Prince Kwame Adjonyoh</t>
+  </si>
+  <si>
+    <t>NEB-FF2</t>
+  </si>
+  <si>
+    <t>Desmond Tenakwah</t>
+  </si>
+  <si>
+    <t>Session, 2 (12:00 PM - 2:00 PM)</t>
+  </si>
+  <si>
+    <t>Appiah Kofi Broni</t>
+  </si>
+  <si>
+    <t>Herbert Kwabena Agbeshie</t>
+  </si>
+  <si>
+    <t>Emmanuel Appenteng / Jonathan Ayama</t>
+  </si>
+  <si>
+    <t>Beatrice Forson</t>
+  </si>
+  <si>
     <t>Sandra Osei</t>
   </si>
   <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Husseini Nimatu</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Nana Adu</t>
-  </si>
-  <si>
-    <t>PB001</t>
-  </si>
-  <si>
-    <t>Kwabena Amankwah Agyemang</t>
-  </si>
-  <si>
-    <t>PB008</t>
-  </si>
-  <si>
-    <t>Ivy Kuukua Sika Bentil</t>
-  </si>
-  <si>
-    <t>PB014</t>
-  </si>
-  <si>
-    <t>Perfect Mawuli Keti</t>
-  </si>
-  <si>
-    <t>PB020</t>
-  </si>
-  <si>
-    <t>Jesse Turkson</t>
-  </si>
-  <si>
-    <t>PB201</t>
-  </si>
-  <si>
-    <t>Lawson Komla Adobor</t>
-  </si>
-  <si>
-    <t>PB208</t>
-  </si>
-  <si>
-    <t>Eric Mensah</t>
-  </si>
-  <si>
-    <t>PB212</t>
-  </si>
-  <si>
-    <t>George Wiafe</t>
-  </si>
-  <si>
-    <t>PB214</t>
-  </si>
-  <si>
-    <t>Josephine Aduku</t>
-  </si>
-  <si>
-    <t>A110</t>
-  </si>
-  <si>
-    <t>Abdulai Fatimah</t>
-  </si>
-  <si>
-    <t>NAF1</t>
-  </si>
-  <si>
-    <t>Christian Kofi Essandoh / Kadzi Daniel</t>
-  </si>
-  <si>
-    <t>NEB-FF1</t>
-  </si>
-  <si>
-    <t>Prince Kwame Adjonyoh</t>
-  </si>
-  <si>
-    <t>NEB-FF2</t>
-  </si>
-  <si>
-    <t>Desmond Tenakwah</t>
-  </si>
-  <si>
-    <t>Session, 2 (12:00 PM - 2:00 PM)</t>
-  </si>
-  <si>
-    <t>Herbert Kwabena Agbeshie</t>
+    <t>Abrefi Faustina</t>
   </si>
   <si>
     <t>Sylvester Adu-Gyamfi</t>
   </si>
   <si>
+    <t>Yanney Taylor Brian</t>
+  </si>
+  <si>
+    <t>Akuako Emmanuel Selasie</t>
+  </si>
+  <si>
+    <t>Asorku Joshua Mawuena</t>
+  </si>
+  <si>
+    <t>Solomon Akumanyin</t>
+  </si>
+  <si>
+    <t>Florence Koomson</t>
+  </si>
+  <si>
+    <t>Maxwell Kofi Adu Junior</t>
+  </si>
+  <si>
+    <t>Catherine Tetteh</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>Tabi Lawrence</t>
+  </si>
+  <si>
+    <t>Ankrah Urmah Bosompem</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>Wafawu Mashud</t>
+  </si>
+  <si>
+    <t>Ethel Abdul Karim / Appiah Gideon Mawuli</t>
+  </si>
+  <si>
+    <t>Maurice Elikem Sunuh</t>
+  </si>
+  <si>
+    <t>Session, 3 (3:00 PM - 5:00 PM)</t>
+  </si>
+  <si>
+    <t>Akoto Kwadwo Gyedu</t>
+  </si>
+  <si>
+    <t>Nesco Nanzie Benjamin</t>
+  </si>
+  <si>
+    <t>Arhin Adwoa Blessing Keren / Paul Osei</t>
+  </si>
+  <si>
+    <t>Erica Amoaa</t>
+  </si>
+  <si>
+    <t>Judah Nambu</t>
+  </si>
+  <si>
+    <t>Asampabila Gideon</t>
+  </si>
+  <si>
+    <t>Lilian Amankwaa</t>
+  </si>
+  <si>
+    <t>Baninipuni Melvin</t>
+  </si>
+  <si>
+    <t>Justina Asiedu Nyarko</t>
+  </si>
+  <si>
+    <t>Yeboah Jacqueline Akua</t>
+  </si>
+  <si>
+    <t>Eugene Odame Asante</t>
+  </si>
+  <si>
+    <t>Agbenu Samuel</t>
+  </si>
+  <si>
+    <t>Prince Owusu</t>
+  </si>
+  <si>
+    <t>Derrick Kofi Kyeremateng</t>
+  </si>
+  <si>
+    <t>Edmund Atta Keborni</t>
+  </si>
+  <si>
+    <t>Felicia Nkansah / Agyapong Bernard Antwi</t>
+  </si>
+  <si>
+    <t>Edmond Khan</t>
+  </si>
+  <si>
+    <t>Lucas Biiyiin</t>
+  </si>
+  <si>
+    <t>NEB-SF</t>
+  </si>
+  <si>
+    <t>Nyarko Felicity Serwaa / Agyekum Kuffour Gideon</t>
+  </si>
+  <si>
+    <t>NEB-TF</t>
+  </si>
+  <si>
+    <t>Bright Eli Semaha / Alfred Ackon</t>
+  </si>
+  <si>
+    <t>Tuesday, 18 August 2026</t>
+  </si>
+  <si>
+    <t>Clement Osei-Agyeman</t>
+  </si>
+  <si>
+    <t>Eugene Akomeah</t>
+  </si>
+  <si>
+    <t>Karis Richardson / Phillip Quarshie</t>
+  </si>
+  <si>
+    <t>Prosper Gyansah Ofosu</t>
+  </si>
+  <si>
+    <t>Doreen A. Fosu Asamoah</t>
+  </si>
+  <si>
+    <t>Kwadwo Baiden-Boafo</t>
+  </si>
+  <si>
+    <t>Papa Tawiah Arthur</t>
+  </si>
+  <si>
+    <t>Dickson Avornor</t>
+  </si>
+  <si>
+    <t>Emmanuel Ayite - Atiapa</t>
+  </si>
+  <si>
+    <t>Magdalene Akua Aseda Obeng Baah</t>
+  </si>
+  <si>
+    <t>Emmanuel Oduro</t>
+  </si>
+  <si>
+    <t>Christopher Tetteh Morton</t>
+  </si>
+  <si>
+    <t>Ephraim Essel / Nana Agyemang Badu</t>
+  </si>
+  <si>
+    <t>Benard Andoh Eshun</t>
+  </si>
+  <si>
+    <t>David Badu</t>
+  </si>
+  <si>
+    <t>Lawrence Cudjoe / Manuel Akuamoah-Boateng</t>
+  </si>
+  <si>
+    <t>Priscilla Cudjoe / Robert Afiakwa Owusu</t>
+  </si>
+  <si>
+    <t>Belazel Owusu</t>
+  </si>
+  <si>
+    <t>Derrick Duah Yeboah</t>
+  </si>
+  <si>
+    <t>Nartey Lamech Narte</t>
+  </si>
+  <si>
+    <t>Barnabas Owusu-Banahene</t>
+  </si>
+  <si>
+    <t>Jemimah Nyarkoa</t>
+  </si>
+  <si>
+    <t>Achala Elijah</t>
+  </si>
+  <si>
+    <t>Henry Tutu Adjei</t>
+  </si>
+  <si>
+    <t>Nana Ampofo Kusi-Mensah</t>
+  </si>
+  <si>
+    <t>Jason Abeiku Boateng Techie</t>
+  </si>
+  <si>
+    <t>Ato Anamoah Essel</t>
+  </si>
+  <si>
+    <t>Nii Lartey</t>
+  </si>
+  <si>
+    <t>Emmanuel Bempong / Godfred Adu Mensah</t>
+  </si>
+  <si>
+    <t>Mathias Vormawor</t>
+  </si>
+  <si>
+    <t>Augustine Gyening</t>
+  </si>
+  <si>
+    <t>Linda Dede Teye</t>
+  </si>
+  <si>
+    <t>Ebenezer Dompreh Marfo</t>
+  </si>
+  <si>
+    <t>Andy Owusu-Boateng / Mansur Abubakar</t>
+  </si>
+  <si>
+    <t>Abubakar Muniru</t>
+  </si>
+  <si>
+    <t>Christie Nyarko</t>
+  </si>
+  <si>
+    <t>David Nkasah Mensah</t>
+  </si>
+  <si>
+    <t>Evans Tignanlene Nkumicha</t>
+  </si>
+  <si>
+    <t>Archer Michaelina Adu</t>
+  </si>
+  <si>
+    <t>Prince Asare Ange Seraphin</t>
+  </si>
+  <si>
+    <t>Isaac Ayensu</t>
+  </si>
+  <si>
+    <t>Lucian Nsiah Sarkodie</t>
+  </si>
+  <si>
+    <t>Prince Nyame</t>
+  </si>
+  <si>
+    <t>Effah Emmanuel</t>
+  </si>
+  <si>
+    <t>Mariwan Aida Yuoda</t>
+  </si>
+  <si>
+    <t>Isaiah Amatey Lawerteh</t>
+  </si>
+  <si>
+    <t>Boakye Godfred Manu Addo</t>
+  </si>
+  <si>
+    <t>Tevia Abigail Mawunyo / Natalie Naa Amorkor Armafio</t>
+  </si>
+  <si>
+    <t>Samuel Agyemang-Duah</t>
+  </si>
+  <si>
+    <t>Christiana Oforiwaa Kodua / Debora Sarpomaa Boateng</t>
+  </si>
+  <si>
+    <t>Alex Ohemeng Adusei / Oliver Kobby Biney</t>
+  </si>
+  <si>
+    <t>Wednesday, 19 August 2026</t>
+  </si>
+  <si>
+    <t>James Eric Ossom / Desmond Tenakwah</t>
+  </si>
+  <si>
+    <t>Farida Yusif</t>
+  </si>
+  <si>
+    <t>Blessing Owusu</t>
+  </si>
+  <si>
+    <t>Emmanuel Gyimah</t>
+  </si>
+  <si>
+    <t>Hannah Sarpong</t>
+  </si>
+  <si>
+    <t>Anyah Elijah Eduah</t>
+  </si>
+  <si>
+    <t>Sylvester Yeboah</t>
+  </si>
+  <si>
+    <t>Osei Sarfo Kantanka</t>
+  </si>
+  <si>
+    <t>Rukaiya Sayeed</t>
+  </si>
+  <si>
+    <t>Adasi Vida Birago</t>
+  </si>
+  <si>
+    <t>Billey Evans</t>
+  </si>
+  <si>
+    <t>Ehud Adjei Yankey</t>
+  </si>
+  <si>
+    <t>Ebenezer Oti Boateng / Benard Kojo Aidoo</t>
+  </si>
+  <si>
+    <t>Prince Kwame Adjonyoh / Kwabena Amankwah Agyemang</t>
+  </si>
+  <si>
+    <t>Asare Ruth / Ntifo Gloria</t>
+  </si>
+  <si>
+    <t>Ivy Kuukua Sika Bentil / Eric Mensah</t>
+  </si>
+  <si>
+    <t>N1</t>
+  </si>
+  <si>
+    <t>N2</t>
+  </si>
+  <si>
+    <t>Christian Kofi Essandoh</t>
+  </si>
+  <si>
+    <t>Ethel Abdul Karim</t>
+  </si>
+  <si>
+    <t>Kadzi Daniel</t>
+  </si>
+  <si>
+    <t>Appiah Gideon Mawuli</t>
+  </si>
+  <si>
+    <t>Emmanuel Appenteng</t>
+  </si>
+  <si>
     <t>Jonathan Ayama / Maurice Elikem Sunuh</t>
   </si>
   <si>
-    <t>Beatrice Forson</t>
-  </si>
-  <si>
-    <t>Abrefi Faustina</t>
-  </si>
-  <si>
-    <t>Emmanuel Appenteng</t>
-  </si>
-  <si>
-    <t>Akuako Emmanuel Selasie</t>
-  </si>
-  <si>
-    <t>Florence Koomson</t>
-  </si>
-  <si>
-    <t>Asorku Joshua Mawuena</t>
-  </si>
-  <si>
-    <t>Solomon Akumanyin</t>
-  </si>
-  <si>
-    <t>Catherine Tetteh</t>
-  </si>
-  <si>
-    <t>Maxwell Kofi Adu Junior</t>
-  </si>
-  <si>
-    <t>Ethel Abdul Karim</t>
-  </si>
-  <si>
-    <t>Yanney Taylor Brian</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>Erica Amoaa</t>
-  </si>
-  <si>
-    <t>Wafawu Mashud</t>
-  </si>
-  <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>Tabi Lawrence</t>
-  </si>
-  <si>
-    <t>Appiah Gideon Mawuli / Ankrah Urmah Bosompem</t>
-  </si>
-  <si>
-    <t>Appiah Kofi Broni</t>
-  </si>
-  <si>
-    <t>Session, 3 (3:00 PM - 5:00 PM)</t>
-  </si>
-  <si>
-    <t>Akoto Kwadwo Gyedu</t>
-  </si>
-  <si>
-    <t>Nesco Nanzie Benjamin</t>
-  </si>
-  <si>
-    <t>Arhin Adwoa Blessing Keren / Paul Osei</t>
-  </si>
-  <si>
-    <t>Erica Winnie Gado</t>
-  </si>
-  <si>
-    <t>Judah Nambu</t>
-  </si>
-  <si>
-    <t>Asampabila Gideon</t>
-  </si>
-  <si>
-    <t>Lilian Amankwaa</t>
-  </si>
-  <si>
-    <t>Baninipuni Melvin</t>
-  </si>
-  <si>
-    <t>Justina Asiedu Nyarko</t>
-  </si>
-  <si>
-    <t>Yeboah Jacqueline Akua</t>
-  </si>
-  <si>
-    <t>Eugene Odame Asante</t>
-  </si>
-  <si>
-    <t>Agbenu Samuel</t>
-  </si>
-  <si>
-    <t>Prince Owusu</t>
-  </si>
-  <si>
-    <t>Derrick Kofi Kyeremateng</t>
-  </si>
-  <si>
-    <t>Edmund Atta Keborni</t>
-  </si>
-  <si>
-    <t>Felicia Nkansah / Agyapong Bernard Antwi</t>
-  </si>
-  <si>
-    <t>Edmond Khan</t>
-  </si>
-  <si>
-    <t>Lucas Biiyiin</t>
-  </si>
-  <si>
-    <t>NEB-SF</t>
-  </si>
-  <si>
-    <t>Nyarko Felicity Serwaa / Agyekum Kuffour Gideon</t>
-  </si>
-  <si>
-    <t>NEB-TF</t>
-  </si>
-  <si>
-    <t>Bright Eli Semaha / Alfred Ackon</t>
-  </si>
-  <si>
-    <t>Tuesday, 18 August 2026</t>
-  </si>
-  <si>
-    <t>Clement Osei-Agyeman</t>
-  </si>
-  <si>
-    <t>Eugene Akomeah</t>
-  </si>
-  <si>
-    <t>Karis Richardson / Phillip Quarshie</t>
-  </si>
-  <si>
-    <t>Prosper Gyansah Ofosu</t>
-  </si>
-  <si>
-    <t>Doreen A. Fosu Asamoah</t>
-  </si>
-  <si>
-    <t>Kwadwo Baiden-Boafo</t>
-  </si>
-  <si>
-    <t>Papa Tawiah Arthur</t>
-  </si>
-  <si>
-    <t>Dickson Avornor</t>
-  </si>
-  <si>
-    <t>Emmanuel Ayite - Atiapa</t>
-  </si>
-  <si>
-    <t>Magdalene Akua Aseda Obeng Baah</t>
-  </si>
-  <si>
-    <t>Emmanuel Oduro</t>
-  </si>
-  <si>
-    <t>Christopher Tetteh Morton</t>
-  </si>
-  <si>
-    <t>Ephraim Essel / Nana Agyemang Badu</t>
-  </si>
-  <si>
-    <t>Benard Andoh Eshun</t>
-  </si>
-  <si>
-    <t>David Badu</t>
-  </si>
-  <si>
-    <t>Lawrence Cudjoe / Manuel Akuamoah-Boateng</t>
-  </si>
-  <si>
-    <t>Priscilla Cudjoe / Robert Afiakwa Owusu</t>
-  </si>
-  <si>
-    <t>Belazel Owusu</t>
-  </si>
-  <si>
-    <t>Derrick Duah Yeboah</t>
-  </si>
-  <si>
-    <t>Nartey Lamech Narte</t>
-  </si>
-  <si>
-    <t>Barnabas Owusu-Banahene</t>
-  </si>
-  <si>
-    <t>Jemimah Nyarkoa</t>
-  </si>
-  <si>
-    <t>Achala Elijah</t>
-  </si>
-  <si>
-    <t>Henry Tutu Adjei</t>
-  </si>
-  <si>
-    <t>Nana Ampofo Kusi-Mensah</t>
-  </si>
-  <si>
-    <t>Jason Abeiku Boateng Techie</t>
-  </si>
-  <si>
-    <t>Ato Anamoah Essel</t>
-  </si>
-  <si>
-    <t>Nii Lartey</t>
-  </si>
-  <si>
-    <t>Emmanuel Bempong / Godfred Adu Mensah</t>
-  </si>
-  <si>
-    <t>Mathias Vormawor</t>
-  </si>
-  <si>
-    <t>Augustine Gyening</t>
-  </si>
-  <si>
-    <t>Linda Dede Teye</t>
-  </si>
-  <si>
-    <t>Ebenezer Dompreh Marfo</t>
-  </si>
-  <si>
-    <t>Andy Owusu-Boateng / Mansur Abubakar</t>
-  </si>
-  <si>
-    <t>Abubakar Muniru</t>
-  </si>
-  <si>
-    <t>Christie Nyarko</t>
-  </si>
-  <si>
-    <t>David Nkasah Mensah</t>
-  </si>
-  <si>
-    <t>Evans Tignanlene Nkumicha</t>
-  </si>
-  <si>
-    <t>Archer Michaelina Adu</t>
-  </si>
-  <si>
-    <t>Prince Asare Ange Seraphin</t>
-  </si>
-  <si>
-    <t>Isaac Ayensu</t>
-  </si>
-  <si>
-    <t>Lucian Nsiah Sarkodie</t>
-  </si>
-  <si>
-    <t>Prince Nyame</t>
-  </si>
-  <si>
-    <t>Effah Emmanuel</t>
-  </si>
-  <si>
-    <t>Mariwan Aida Yuoda</t>
-  </si>
-  <si>
-    <t>Isaiah Amatey Lawerteh</t>
-  </si>
-  <si>
-    <t>Boakye Godfred Manu Addo</t>
-  </si>
-  <si>
-    <t>Tevia Abigail Mawunyo / Natalie Naa Amorkor Armafio</t>
-  </si>
-  <si>
-    <t>Samuel Agyemang-Duah</t>
-  </si>
-  <si>
-    <t>Christiana Oforiwaa Kodua / Debora Sarpomaa Boateng</t>
-  </si>
-  <si>
-    <t>Alex Ohemeng Adusei / Oliver Kobby Biney</t>
-  </si>
-  <si>
-    <t>Wednesday, 19 August 2026</t>
-  </si>
-  <si>
-    <t>James Eric Ossom / Desmond Tenakwah</t>
-  </si>
-  <si>
-    <t>Farida Yusif</t>
-  </si>
-  <si>
-    <t>Blessing Owusu</t>
-  </si>
-  <si>
-    <t>Emmanuel Gyimah</t>
-  </si>
-  <si>
-    <t>Hannah Sarpong</t>
-  </si>
-  <si>
-    <t>Anyah Elijah Eduah</t>
-  </si>
-  <si>
-    <t>Sylvester Yeboah</t>
-  </si>
-  <si>
-    <t>Osei Sarfo Kantanka</t>
-  </si>
-  <si>
-    <t>Rukaiya Sayeed</t>
-  </si>
-  <si>
-    <t>Adasi Vida Birago</t>
-  </si>
-  <si>
-    <t>Billey Evans</t>
-  </si>
-  <si>
-    <t>Ehud Adjei Yankey</t>
-  </si>
-  <si>
-    <t>Ebenezer Oti Boateng / Benard Kojo Aidoo</t>
-  </si>
-  <si>
-    <t>Prince Kwame Adjonyoh / Kwabena Amankwah Agyemang</t>
-  </si>
-  <si>
-    <t>Asare Ruth / Ntifo Gloria</t>
+    <t>Sylvester Adu-Gyamfi / Akuako Emmanuel Selasie</t>
+  </si>
+  <si>
+    <t>Appiah Kofi Broni / Herbert Kwabena Agbeshie</t>
+  </si>
+  <si>
+    <t>Arhin Adwoa Blessing Keren</t>
+  </si>
+  <si>
+    <t>Tabi Lawrence / Erica Amoaa</t>
+  </si>
+  <si>
+    <t>Paul Osei</t>
+  </si>
+  <si>
+    <t>Nyarko Felicity Serwaa</t>
+  </si>
+  <si>
+    <t>Agyekum Kuffour Gideon</t>
+  </si>
+  <si>
+    <t>Bright Eli Semaha</t>
+  </si>
+  <si>
+    <t>Alfred Ackon / Asampabila Gideon</t>
+  </si>
+  <si>
+    <t>Felicia Nkansah</t>
+  </si>
+  <si>
+    <t>Agbenu Samuel / Lilian Amankwaa</t>
+  </si>
+  <si>
+    <t>Justina Asiedu Nyarko / Yeboah Jacqueline Akua</t>
+  </si>
+  <si>
+    <t>Thursday, 20 August 2026</t>
+  </si>
+  <si>
+    <t>Ephraim Essel</t>
+  </si>
+  <si>
+    <t>Phillip Quarshie / Clement Osei-Agyeman</t>
+  </si>
+  <si>
+    <t>Agyapong Bernard Antwi</t>
+  </si>
+  <si>
+    <t>Lawrence Cudjoe</t>
+  </si>
+  <si>
+    <t>Manuel Akuamoah-Boateng</t>
+  </si>
+  <si>
+    <t>Edmund Atta Keborni / Prince Owusu</t>
+  </si>
+  <si>
+    <t>Karis Richardson</t>
+  </si>
+  <si>
+    <t>Nana Agyemang Badu / Christopher Tetteh Morton</t>
+  </si>
+  <si>
+    <t>Emmanuel Bempong</t>
+  </si>
+  <si>
+    <t>Barnabas Owusu-Banahene / Nana Ampofo Kusi-Mensah</t>
+  </si>
+  <si>
+    <t>Priscilla Cudjoe</t>
+  </si>
+  <si>
+    <t>Robert Afiakwa Owusu</t>
+  </si>
+  <si>
+    <t>Godfred Adu Mensah</t>
+  </si>
+  <si>
+    <t>Mathias Vormawor / Nii Lartey</t>
+  </si>
+  <si>
+    <t>Isaac Ayensu / Lucian Nsiah Sarkodie</t>
+  </si>
+  <si>
+    <t>Christiana Oforiwaa Kodua</t>
+  </si>
+  <si>
+    <t>Andy Owusu-Boateng</t>
+  </si>
+  <si>
+    <t>Debora Sarpomaa Boateng</t>
+  </si>
+  <si>
+    <t>Mansur Abubakar</t>
+  </si>
+  <si>
+    <t>Oliver Kobby Biney</t>
+  </si>
+  <si>
+    <t>Effah Emmanuel / Alex Ohemeng Adusei</t>
+  </si>
+  <si>
+    <t>Friday, 21 August 2026</t>
+  </si>
+  <si>
+    <t>Boakye Godfred Manu Addo / Isaiah Amatey Lawerteh</t>
+  </si>
+  <si>
+    <t>Tevia Abigail Mawunyo</t>
+  </si>
+  <si>
+    <t>Natalie Naa Amorkor Armafio</t>
+  </si>
+  <si>
+    <t>Ebenezer Oti Boateng</t>
+  </si>
+  <si>
+    <t>Benard Kojo Aidoo</t>
+  </si>
+  <si>
+    <t>Osei Sarfo Kantanka / Erica Winnie Gado</t>
+  </si>
+  <si>
+    <t>Anyah Elijah Eduah / Sylvester Yeboah</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>Josephine Aduku / Ivy Kuukua Sika Bentil</t>
+  </si>
+  <si>
+    <t>Kadzi Daniel / Abdulai Fatimah</t>
+  </si>
+  <si>
+    <t>Alfred Ackon</t>
+  </si>
+  <si>
+    <t>Wafawu Mashud / Tabi Lawrence</t>
+  </si>
+  <si>
+    <t>Jonathan Ayama</t>
+  </si>
+  <si>
+    <t>Nesco Nanzie Benjamin / Edmond Khan</t>
+  </si>
+  <si>
+    <t>Lucas Biiyiin / Nyarko Felicity Serwaa</t>
+  </si>
+  <si>
+    <t>Monday, 24 August 2026</t>
+  </si>
+  <si>
+    <t>Lilian Amankwaa / Eugene Odame Asante</t>
+  </si>
+  <si>
+    <t>Derrick Kofi Kyeremateng / Edmund Atta Keborni</t>
+  </si>
+  <si>
+    <t>Robert Afiakwa Owusu / Barnabas Owusu-Banahene</t>
+  </si>
+  <si>
+    <t>Phillip Quarshie</t>
+  </si>
+  <si>
+    <t>Clement Osei-Agyeman / Eugene Akomeah</t>
+  </si>
+  <si>
+    <t>Nana Agyemang Badu</t>
+  </si>
+  <si>
+    <t>Nartey Lamech Narte / Jemimah Nyarkoa</t>
+  </si>
+  <si>
+    <t>Nii Lartey / Ato Anamoah Essel</t>
+  </si>
+  <si>
+    <t>Tuesday, 25 August 2026</t>
+  </si>
+  <si>
+    <t>Alex Ohemeng Adusei</t>
+  </si>
+  <si>
+    <t>Archer Michaelina Adu / Prince Nyame</t>
+  </si>
+  <si>
+    <t>Linda Dede Teye / Ebenezer Dompreh Marfo</t>
+  </si>
+  <si>
+    <t>Asare Ruth</t>
+  </si>
+  <si>
+    <t>Nana Adu / Rukaiya Sayeed</t>
+  </si>
+  <si>
+    <t>Maurice Elikem Sunuh / Appiah Kofi Broni</t>
+  </si>
+  <si>
+    <t>Solomon Akumanyin / Catherine Tetteh</t>
+  </si>
+  <si>
+    <t>Wednesday, 26 August 2026</t>
+  </si>
+  <si>
+    <t>Baninipuni Melvin / Justina Asiedu Nyarko</t>
+  </si>
+  <si>
+    <t>Kwadwo Baiden-Boafo / Karis Richardson</t>
+  </si>
+  <si>
+    <t>Thursday, 27 August 2026</t>
+  </si>
+  <si>
+    <t>Blessing Owusu / Emmanuel Gyimah</t>
+  </si>
+  <si>
+    <t>Ehud Adjei Yankey / Billey Evans</t>
+  </si>
+  <si>
+    <t>Friday, 28 August 2026</t>
+  </si>
+  <si>
+    <t>Paul Osei / Akoto Kwadwo Gyedu</t>
+  </si>
+  <si>
+    <t>Erica Amoaa / Judah Nambu</t>
+  </si>
+  <si>
+    <t>Prince Owusu / Prosper Gyansah Ofosu</t>
+  </si>
+  <si>
+    <t>Monday, 31 August 2026</t>
+  </si>
+  <si>
+    <t>David Badu / Belazel Owusu</t>
+  </si>
+  <si>
+    <t>Lucian Nsiah Sarkodie / Mariwan Aida Yuoda</t>
+  </si>
+  <si>
+    <t>Christie Nyarko / David Nkasah Mensah</t>
+  </si>
+  <si>
+    <t>Mansur Abubakar / Prince Asare Ange Seraphin</t>
+  </si>
+  <si>
+    <t>Achala Elijah / Abubakar Muniru</t>
+  </si>
+  <si>
+    <t>Samuel Agyemang-Duah / Farida Yusif</t>
+  </si>
+  <si>
+    <t>Erica Winnie Gado / Beatrice Forson</t>
+  </si>
+  <si>
+    <t>Adasi Vida Birago / Hannah Sarpong</t>
+  </si>
+  <si>
+    <t>Tuesday, 1 September 2026</t>
   </si>
   <si>
     <t>Eric Mensah / George Wiafe</t>
   </si>
   <si>
-    <t>N1</t>
-  </si>
-  <si>
-    <t>Christian Kofi Essandoh</t>
-  </si>
-  <si>
-    <t>N2</t>
-  </si>
-  <si>
-    <t>Kadzi Daniel</t>
-  </si>
-  <si>
-    <t>Appiah Gideon Mawuli</t>
-  </si>
-  <si>
-    <t>Ankrah Urmah Bosompem</t>
-  </si>
-  <si>
-    <t>Jonathan Ayama</t>
-  </si>
-  <si>
-    <t>Maurice Elikem Sunuh / Appiah Kofi Broni</t>
-  </si>
-  <si>
-    <t>Akuako Emmanuel Selasie / Asorku Joshua Mawuena</t>
-  </si>
-  <si>
-    <t>Herbert Kwabena Agbeshie / Sylvester Adu-Gyamfi</t>
-  </si>
-  <si>
-    <t>Arhin Adwoa Blessing Keren</t>
-  </si>
-  <si>
-    <t>Tabi Lawrence / Erica Amoaa</t>
-  </si>
-  <si>
-    <t>Paul Osei</t>
-  </si>
-  <si>
-    <t>Nyarko Felicity Serwaa</t>
-  </si>
-  <si>
-    <t>Agyekum Kuffour Gideon</t>
-  </si>
-  <si>
-    <t>Bright Eli Semaha</t>
-  </si>
-  <si>
-    <t>Alfred Ackon / Asampabila Gideon</t>
-  </si>
-  <si>
-    <t>Felicia Nkansah</t>
-  </si>
-  <si>
-    <t>Agbenu Samuel / Lilian Amankwaa</t>
-  </si>
-  <si>
-    <t>Justina Asiedu Nyarko / Yeboah Jacqueline Akua</t>
-  </si>
-  <si>
-    <t>Thursday, 20 August 2026</t>
-  </si>
-  <si>
-    <t>Ephraim Essel</t>
-  </si>
-  <si>
-    <t>Phillip Quarshie / Clement Osei-Agyeman</t>
-  </si>
-  <si>
-    <t>Agyapong Bernard Antwi</t>
-  </si>
-  <si>
-    <t>Lawrence Cudjoe</t>
-  </si>
-  <si>
-    <t>Manuel Akuamoah-Boateng</t>
-  </si>
-  <si>
-    <t>Edmund Atta Keborni / Prince Owusu</t>
-  </si>
-  <si>
-    <t>Karis Richardson</t>
-  </si>
-  <si>
-    <t>Nana Agyemang Badu / Christopher Tetteh Morton</t>
-  </si>
-  <si>
-    <t>Emmanuel Bempong</t>
-  </si>
-  <si>
-    <t>Barnabas Owusu-Banahene / Nana Ampofo Kusi-Mensah</t>
-  </si>
-  <si>
-    <t>Priscilla Cudjoe</t>
-  </si>
-  <si>
-    <t>Robert Afiakwa Owusu</t>
-  </si>
-  <si>
-    <t>Godfred Adu Mensah</t>
-  </si>
-  <si>
-    <t>Mathias Vormawor / Nii Lartey</t>
-  </si>
-  <si>
-    <t>Isaac Ayensu / Lucian Nsiah Sarkodie</t>
-  </si>
-  <si>
-    <t>Christiana Oforiwaa Kodua</t>
-  </si>
-  <si>
-    <t>Andy Owusu-Boateng</t>
-  </si>
-  <si>
-    <t>Debora Sarpomaa Boateng</t>
-  </si>
-  <si>
-    <t>Mansur Abubakar</t>
-  </si>
-  <si>
-    <t>Oliver Kobby Biney</t>
-  </si>
-  <si>
-    <t>Effah Emmanuel / Alex Ohemeng Adusei</t>
-  </si>
-  <si>
-    <t>Friday, 21 August 2026</t>
-  </si>
-  <si>
-    <t>Boakye Godfred Manu Addo / Isaiah Amatey Lawerteh</t>
-  </si>
-  <si>
-    <t>Tevia Abigail Mawunyo</t>
-  </si>
-  <si>
-    <t>Natalie Naa Amorkor Armafio</t>
-  </si>
-  <si>
-    <t>Ebenezer Oti Boateng</t>
-  </si>
-  <si>
-    <t>Benard Kojo Aidoo</t>
-  </si>
-  <si>
-    <t>Osei Sarfo Kantanka / Sandra Osei</t>
-  </si>
-  <si>
-    <t>Anyah Elijah Eduah / Sylvester Yeboah</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>Ivy Kuukua Sika Bentil / Eric Mensah</t>
-  </si>
-  <si>
-    <t>Abdulai Fatimah / Abrefi Faustina</t>
-  </si>
-  <si>
-    <t>Alfred Ackon</t>
-  </si>
-  <si>
-    <t>Wafawu Mashud / Tabi Lawrence</t>
-  </si>
-  <si>
-    <t>Maurice Elikem Sunuh</t>
-  </si>
-  <si>
-    <t>Nesco Nanzie Benjamin / Edmond Khan</t>
-  </si>
-  <si>
-    <t>Lucas Biiyiin / Nyarko Felicity Serwaa</t>
-  </si>
-  <si>
-    <t>Monday, 24 August 2026</t>
-  </si>
-  <si>
-    <t>Lilian Amankwaa / Eugene Odame Asante</t>
-  </si>
-  <si>
-    <t>Derrick Kofi Kyeremateng / Edmund Atta Keborni</t>
-  </si>
-  <si>
-    <t>Robert Afiakwa Owusu / Barnabas Owusu-Banahene</t>
-  </si>
-  <si>
-    <t>Phillip Quarshie</t>
-  </si>
-  <si>
-    <t>Clement Osei-Agyeman / Eugene Akomeah</t>
-  </si>
-  <si>
-    <t>Nana Agyemang Badu</t>
-  </si>
-  <si>
-    <t>Nartey Lamech Narte / Jemimah Nyarkoa</t>
-  </si>
-  <si>
-    <t>Nii Lartey / Ato Anamoah Essel</t>
-  </si>
-  <si>
-    <t>Tuesday, 25 August 2026</t>
-  </si>
-  <si>
-    <t>Alex Ohemeng Adusei</t>
-  </si>
-  <si>
-    <t>Archer Michaelina Adu / Prince Nyame</t>
-  </si>
-  <si>
-    <t>Linda Dede Teye / Ebenezer Dompreh Marfo</t>
-  </si>
-  <si>
-    <t>Desmond Tenakwah / Prince Kwame Adjonyoh</t>
-  </si>
-  <si>
-    <t>Solomon Akumanyin / Catherine Tetteh</t>
-  </si>
-  <si>
-    <t>Wednesday, 26 August 2026</t>
-  </si>
-  <si>
-    <t>Ethel Abdul Karim / Appiah Gideon Mawuli</t>
-  </si>
-  <si>
-    <t>Baninipuni Melvin / Justina Asiedu Nyarko</t>
-  </si>
-  <si>
-    <t>Kwadwo Baiden-Boafo / Karis Richardson</t>
-  </si>
-  <si>
-    <t>Thursday, 27 August 2026</t>
-  </si>
-  <si>
-    <t>Blessing Owusu / Emmanuel Gyimah</t>
-  </si>
-  <si>
-    <t>Ehud Adjei Yankey / Billey Evans</t>
-  </si>
-  <si>
-    <t>Friday, 28 August 2026</t>
-  </si>
-  <si>
-    <t>Kadzi Daniel / Abdulai Fatimah</t>
-  </si>
-  <si>
-    <t>Paul Osei / Akoto Kwadwo Gyedu</t>
-  </si>
-  <si>
-    <t>Erica Amoaa / Judah Nambu</t>
-  </si>
-  <si>
-    <t>Prince Owusu / Prosper Gyansah Ofosu</t>
-  </si>
-  <si>
-    <t>Monday, 31 August 2026</t>
-  </si>
-  <si>
-    <t>David Badu / Belazel Owusu</t>
-  </si>
-  <si>
-    <t>Lucian Nsiah Sarkodie / Mariwan Aida Yuoda</t>
-  </si>
-  <si>
-    <t>Christie Nyarko / David Nkasah Mensah</t>
-  </si>
-  <si>
-    <t>Mansur Abubakar / Prince Asare Ange Seraphin</t>
-  </si>
-  <si>
-    <t>Achala Elijah / Abubakar Muniru</t>
-  </si>
-  <si>
-    <t>Samuel Agyemang-Duah / Farida Yusif</t>
-  </si>
-  <si>
-    <t>Asare Ruth</t>
-  </si>
-  <si>
-    <t>Beatrice Forson / Sandra Osei</t>
-  </si>
-  <si>
-    <t>Adasi Vida Birago / Hannah Sarpong</t>
-  </si>
-  <si>
-    <t>Tuesday, 1 September 2026</t>
-  </si>
-  <si>
-    <t>George Wiafe / Christian Kofi Essandoh</t>
+    <t>Jesse Turkson / Lawson Komla Adobor</t>
+  </si>
+  <si>
+    <t>Kwabena Amankwah Agyemang / Perfect Mawuli Keti</t>
+  </si>
+  <si>
+    <t>Agyapong Bernard Antwi / Derrick Kofi Kyeremateng</t>
+  </si>
+  <si>
+    <t>Wednesday, 2 September 2026</t>
+  </si>
+  <si>
+    <t>Augustine Gyening / Mathias Vormawor</t>
+  </si>
+  <si>
+    <t>Debora Sarpomaa Boateng / Andy Owusu-Boateng</t>
+  </si>
+  <si>
+    <t>Mariwan Aida Yuoda / Christiana Oforiwaa Kodua</t>
+  </si>
+  <si>
+    <t>Thursday, 3 September 2026</t>
+  </si>
+  <si>
+    <t>Husseini Nimatu / Nana Adu</t>
   </si>
   <si>
     <t>Lawson Komla Adobor / Josephine Aduku</t>
-  </si>
-  <si>
-    <t>Perfect Mawuli Keti / Jesse Turkson</t>
-  </si>
-  <si>
-    <t>Akoto Kwadwo Gyedu / Nesco Nanzie Benjamin</t>
-  </si>
-  <si>
-    <t>Agyapong Bernard Antwi / Derrick Kofi Kyeremateng</t>
-  </si>
-  <si>
-    <t>Wednesday, 2 September 2026</t>
-  </si>
-  <si>
-    <t>Augustine Gyening / Mathias Vormawor</t>
-  </si>
-  <si>
-    <t>Debora Sarpomaa Boateng / Andy Owusu-Boateng</t>
-  </si>
-  <si>
-    <t>Mariwan Aida Yuoda / Christiana Oforiwaa Kodua</t>
-  </si>
-  <si>
-    <t>Thursday, 3 September 2026</t>
-  </si>
-  <si>
-    <t>Husseini Nimatu / Nana Adu</t>
-  </si>
-  <si>
-    <t>Appiah Kofi Broni / Herbert Kwabena Agbeshie</t>
   </si>
   <si>
     <t>Asampabila Gideon / Baninipuni Melvin</t>
@@ -2448,7 +2442,7 @@
         <v>14</v>
       </c>
       <c r="B165" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -2456,15 +2450,15 @@
         <v>154</v>
       </c>
       <c r="B166" t="s">
-        <v>155</v>
+        <v>29</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>155</v>
+      </c>
+      <c r="B167" t="s">
         <v>156</v>
-      </c>
-      <c r="B167" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -2480,7 +2474,7 @@
         <v>18</v>
       </c>
       <c r="B169" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -2504,7 +2498,7 @@
         <v>24</v>
       </c>
       <c r="B172" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -2528,7 +2522,7 @@
         <v>30</v>
       </c>
       <c r="B175" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -2636,7 +2630,7 @@
         <v>10</v>
       </c>
       <c r="B190" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -2644,7 +2638,7 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -3424,7 +3418,7 @@
         <v>204</v>
       </c>
       <c r="B296" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
@@ -3432,7 +3426,7 @@
         <v>4</v>
       </c>
       <c r="B297" t="s">
-        <v>155</v>
+        <v>29</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
@@ -3440,7 +3434,7 @@
         <v>6</v>
       </c>
       <c r="B298" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
@@ -3464,7 +3458,7 @@
         <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
@@ -3472,7 +3466,7 @@
         <v>14</v>
       </c>
       <c r="B302" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
@@ -3480,7 +3474,7 @@
         <v>16</v>
       </c>
       <c r="B303" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
@@ -3488,7 +3482,7 @@
         <v>18</v>
       </c>
       <c r="B304" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
@@ -3496,7 +3490,7 @@
         <v>20</v>
       </c>
       <c r="B305" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
@@ -3504,7 +3498,7 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
@@ -3512,7 +3506,7 @@
         <v>24</v>
       </c>
       <c r="B307" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
@@ -3520,7 +3514,7 @@
         <v>26</v>
       </c>
       <c r="B308" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
@@ -3528,7 +3522,7 @@
         <v>30</v>
       </c>
       <c r="B309" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
@@ -3580,7 +3574,7 @@
         <v>204</v>
       </c>
       <c r="B317" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
@@ -3588,7 +3582,7 @@
         <v>4</v>
       </c>
       <c r="B318" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
@@ -3612,7 +3606,7 @@
         <v>10</v>
       </c>
       <c r="B321" t="s">
-        <v>66</v>
+        <v>209</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
@@ -3620,7 +3614,7 @@
         <v>12</v>
       </c>
       <c r="B322" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -3628,7 +3622,7 @@
         <v>14</v>
       </c>
       <c r="B323" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
@@ -3636,15 +3630,15 @@
         <v>154</v>
       </c>
       <c r="B324" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B325" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
@@ -3652,7 +3646,7 @@
         <v>16</v>
       </c>
       <c r="B326" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -3660,7 +3654,7 @@
         <v>18</v>
       </c>
       <c r="B327" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
@@ -3668,7 +3662,7 @@
         <v>20</v>
       </c>
       <c r="B328" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
@@ -3676,7 +3670,7 @@
         <v>22</v>
       </c>
       <c r="B329" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
@@ -3684,7 +3678,7 @@
         <v>24</v>
       </c>
       <c r="B330" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -3692,7 +3686,7 @@
         <v>26</v>
       </c>
       <c r="B331" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -3700,7 +3694,7 @@
         <v>28</v>
       </c>
       <c r="B332" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
@@ -3708,7 +3702,7 @@
         <v>30</v>
       </c>
       <c r="B333" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
@@ -3732,7 +3726,7 @@
         <v>58</v>
       </c>
       <c r="B336" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
@@ -4440,7 +4434,7 @@
         <v>204</v>
       </c>
       <c r="B432" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
@@ -4448,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="B433" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
@@ -4456,7 +4450,7 @@
         <v>6</v>
       </c>
       <c r="B434" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
@@ -4464,7 +4458,7 @@
         <v>8</v>
       </c>
       <c r="B435" t="s">
-        <v>225</v>
+        <v>138</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
@@ -4480,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="B437" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
@@ -4488,7 +4482,7 @@
         <v>18</v>
       </c>
       <c r="B438" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
@@ -4496,7 +4490,7 @@
         <v>20</v>
       </c>
       <c r="B439" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
@@ -4504,7 +4498,7 @@
         <v>22</v>
       </c>
       <c r="B440" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
@@ -4512,7 +4506,7 @@
         <v>24</v>
       </c>
       <c r="B441" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
@@ -4520,7 +4514,7 @@
         <v>28</v>
       </c>
       <c r="B442" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
@@ -4528,7 +4522,7 @@
         <v>30</v>
       </c>
       <c r="B443" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
@@ -4536,7 +4530,7 @@
         <v>32</v>
       </c>
       <c r="B444" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
@@ -4544,7 +4538,7 @@
         <v>58</v>
       </c>
       <c r="B445" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
@@ -4552,7 +4546,7 @@
         <v>34</v>
       </c>
       <c r="B446" t="s">
-        <v>9</v>
+        <v>226</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
@@ -4596,7 +4590,7 @@
         <v>204</v>
       </c>
       <c r="B453" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
@@ -4604,7 +4598,7 @@
         <v>4</v>
       </c>
       <c r="B454" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
@@ -4612,7 +4606,7 @@
         <v>6</v>
       </c>
       <c r="B455" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
@@ -4620,7 +4614,7 @@
         <v>8</v>
       </c>
       <c r="B456" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
@@ -4628,7 +4622,7 @@
         <v>12</v>
       </c>
       <c r="B457" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
@@ -4644,7 +4638,7 @@
         <v>18</v>
       </c>
       <c r="B459" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
@@ -4652,7 +4646,7 @@
         <v>20</v>
       </c>
       <c r="B460" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
@@ -4660,7 +4654,7 @@
         <v>22</v>
       </c>
       <c r="B461" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
@@ -4676,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="B463" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
@@ -4684,7 +4678,7 @@
         <v>32</v>
       </c>
       <c r="B464" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
@@ -4692,7 +4686,7 @@
         <v>58</v>
       </c>
       <c r="B465" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
@@ -4700,7 +4694,7 @@
         <v>34</v>
       </c>
       <c r="B466" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
@@ -4716,12 +4710,12 @@
         <v>38</v>
       </c>
       <c r="B468" t="s">
-        <v>160</v>
+        <v>209</v>
       </c>
     </row>
     <row r="470" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B470" s="1"/>
     </row>
@@ -4744,7 +4738,7 @@
         <v>204</v>
       </c>
       <c r="B473" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
@@ -4752,7 +4746,7 @@
         <v>8</v>
       </c>
       <c r="B474" t="s">
-        <v>228</v>
+        <v>60</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
@@ -4760,7 +4754,7 @@
         <v>12</v>
       </c>
       <c r="B475" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
@@ -4768,7 +4762,7 @@
         <v>14</v>
       </c>
       <c r="B476" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
@@ -4832,7 +4826,7 @@
         <v>58</v>
       </c>
       <c r="B484" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
@@ -4861,7 +4855,7 @@
     </row>
     <row r="489" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B489" s="1"/>
     </row>
@@ -5004,12 +4998,12 @@
         <v>83</v>
       </c>
       <c r="B507" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="509" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B509" s="1"/>
     </row>
@@ -5048,7 +5042,7 @@
         <v>8</v>
       </c>
       <c r="B514" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.25">
@@ -5157,7 +5151,7 @@
     </row>
     <row r="529" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B529" s="1"/>
     </row>
@@ -5321,7 +5315,7 @@
     </row>
     <row r="551" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B551" s="1"/>
     </row>
@@ -5456,7 +5450,7 @@
         <v>34</v>
       </c>
       <c r="B568" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.25">
@@ -5488,12 +5482,12 @@
         <v>83</v>
       </c>
       <c r="B572" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="574" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B574" s="1"/>
     </row>
@@ -5548,7 +5542,7 @@
         <v>18</v>
       </c>
       <c r="B581" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.25">
@@ -5580,7 +5574,7 @@
         <v>55</v>
       </c>
       <c r="B585" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.25">
@@ -5588,7 +5582,7 @@
         <v>32</v>
       </c>
       <c r="B586" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.25">
@@ -5596,7 +5590,7 @@
         <v>58</v>
       </c>
       <c r="B587" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.25">
@@ -5604,7 +5598,7 @@
         <v>34</v>
       </c>
       <c r="B588" t="s">
-        <v>9</v>
+        <v>226</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.25">
@@ -5612,7 +5606,7 @@
         <v>36</v>
       </c>
       <c r="B589" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.25">
@@ -5620,12 +5614,12 @@
         <v>38</v>
       </c>
       <c r="B590" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="592" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B592" s="1"/>
     </row>
@@ -5648,7 +5642,7 @@
         <v>204</v>
       </c>
       <c r="B595" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.25">
@@ -5656,7 +5650,7 @@
         <v>4</v>
       </c>
       <c r="B596" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.25">
@@ -5664,7 +5658,7 @@
         <v>6</v>
       </c>
       <c r="B597" t="s">
-        <v>160</v>
+        <v>209</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.25">
@@ -5672,7 +5666,7 @@
         <v>8</v>
       </c>
       <c r="B598" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.25">
@@ -5736,7 +5730,7 @@
         <v>28</v>
       </c>
       <c r="B606" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.25">
@@ -5752,7 +5746,7 @@
         <v>32</v>
       </c>
       <c r="B608" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.25">
@@ -5760,7 +5754,7 @@
         <v>58</v>
       </c>
       <c r="B609" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.25">
@@ -5768,7 +5762,7 @@
         <v>34</v>
       </c>
       <c r="B610" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.25">
@@ -5776,7 +5770,7 @@
         <v>36</v>
       </c>
       <c r="B611" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.25">
@@ -5784,12 +5778,12 @@
         <v>38</v>
       </c>
       <c r="B612" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="614" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B614" s="1"/>
     </row>
@@ -5828,7 +5822,7 @@
         <v>10</v>
       </c>
       <c r="B619" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.25">
@@ -5836,7 +5830,7 @@
         <v>12</v>
       </c>
       <c r="B620" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.25">
@@ -5844,7 +5838,7 @@
         <v>14</v>
       </c>
       <c r="B621" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.25">
@@ -5852,7 +5846,7 @@
         <v>16</v>
       </c>
       <c r="B622" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.25">
@@ -5860,7 +5854,7 @@
         <v>20</v>
       </c>
       <c r="B623" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.25">
@@ -5868,7 +5862,7 @@
         <v>22</v>
       </c>
       <c r="B624" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
@@ -5876,7 +5870,7 @@
         <v>24</v>
       </c>
       <c r="B625" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.25">
@@ -5884,7 +5878,7 @@
         <v>30</v>
       </c>
       <c r="B626" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.25">
@@ -5937,7 +5931,7 @@
     </row>
     <row r="634" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B634" s="1"/>
     </row>
@@ -6300,7 +6294,7 @@
         <v>83</v>
       </c>
       <c r="B681" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="683" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6564,7 +6558,7 @@
         <v>18</v>
       </c>
       <c r="B717" t="s">
-        <v>146</v>
+        <v>15</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.25">
@@ -6604,7 +6598,7 @@
         <v>28</v>
       </c>
       <c r="B722" t="s">
-        <v>246</v>
+        <v>146</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.25">
@@ -6620,7 +6614,7 @@
         <v>32</v>
       </c>
       <c r="B724" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.25">
@@ -6628,7 +6622,7 @@
         <v>58</v>
       </c>
       <c r="B725" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.25">
@@ -6636,7 +6630,7 @@
         <v>34</v>
       </c>
       <c r="B726" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.25">
@@ -6644,12 +6638,12 @@
         <v>81</v>
       </c>
       <c r="B727" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="729" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B729" s="1"/>
     </row>
@@ -6672,7 +6666,7 @@
         <v>204</v>
       </c>
       <c r="B732" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.25">
@@ -6680,7 +6674,7 @@
         <v>4</v>
       </c>
       <c r="B733" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.25">
@@ -6688,7 +6682,7 @@
         <v>6</v>
       </c>
       <c r="B734" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.25">
@@ -6696,7 +6690,7 @@
         <v>8</v>
       </c>
       <c r="B735" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.25">
@@ -6704,7 +6698,7 @@
         <v>10</v>
       </c>
       <c r="B736" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.25">
@@ -6712,7 +6706,7 @@
         <v>12</v>
       </c>
       <c r="B737" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.25">
@@ -6720,7 +6714,7 @@
         <v>16</v>
       </c>
       <c r="B738" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.25">
@@ -6736,7 +6730,7 @@
         <v>20</v>
       </c>
       <c r="B740" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
@@ -6744,7 +6738,7 @@
         <v>22</v>
       </c>
       <c r="B741" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.25">
@@ -6808,7 +6802,7 @@
         <v>36</v>
       </c>
       <c r="B749" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
@@ -6816,7 +6810,7 @@
         <v>38</v>
       </c>
       <c r="B750" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.25">
@@ -6824,7 +6818,7 @@
         <v>81</v>
       </c>
       <c r="B751" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.25">
@@ -6832,12 +6826,12 @@
         <v>83</v>
       </c>
       <c r="B752" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="754" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B754" s="1"/>
     </row>
@@ -6860,7 +6854,7 @@
         <v>204</v>
       </c>
       <c r="B757" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.25">
@@ -6868,7 +6862,7 @@
         <v>4</v>
       </c>
       <c r="B758" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.25">
@@ -6876,7 +6870,7 @@
         <v>6</v>
       </c>
       <c r="B759" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.25">
@@ -6884,7 +6878,7 @@
         <v>8</v>
       </c>
       <c r="B760" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.25">
@@ -6924,7 +6918,7 @@
         <v>24</v>
       </c>
       <c r="B765" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.25">
@@ -6948,7 +6942,7 @@
         <v>32</v>
       </c>
       <c r="B768" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.25">
@@ -6956,7 +6950,7 @@
         <v>58</v>
       </c>
       <c r="B769" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.25">
@@ -6964,7 +6958,7 @@
         <v>34</v>
       </c>
       <c r="B770" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.25">
@@ -6985,7 +6979,7 @@
     </row>
     <row r="774" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B774" s="1"/>
     </row>
@@ -7040,7 +7034,7 @@
         <v>10</v>
       </c>
       <c r="B781" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.25">
@@ -7120,7 +7114,7 @@
         <v>34</v>
       </c>
       <c r="B791" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.25">
@@ -7149,7 +7143,7 @@
     </row>
     <row r="796" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B796" s="1"/>
     </row>
@@ -7305,7 +7299,7 @@
     </row>
     <row r="817" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B817" s="1"/>
     </row>
@@ -7352,7 +7346,7 @@
         <v>8</v>
       </c>
       <c r="B823" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.25">
@@ -7472,7 +7466,7 @@
         <v>81</v>
       </c>
       <c r="B838" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.25">
@@ -7480,12 +7474,12 @@
         <v>83</v>
       </c>
       <c r="B839" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="841" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A841" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B841" s="1"/>
     </row>
@@ -7532,7 +7526,7 @@
         <v>8</v>
       </c>
       <c r="B847" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.25">
@@ -7641,7 +7635,7 @@
     </row>
     <row r="862" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B862" s="1"/>
     </row>
@@ -7672,7 +7666,7 @@
         <v>4</v>
       </c>
       <c r="B866" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.25">
@@ -7688,7 +7682,7 @@
         <v>8</v>
       </c>
       <c r="B868" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.25">
@@ -7760,7 +7754,7 @@
         <v>28</v>
       </c>
       <c r="B877" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.25">
@@ -7800,7 +7794,7 @@
         <v>81</v>
       </c>
       <c r="B882" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.25">
@@ -7808,12 +7802,12 @@
         <v>83</v>
       </c>
       <c r="B883" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="885" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A885" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B885" s="1"/>
     </row>
@@ -7860,7 +7854,7 @@
         <v>8</v>
       </c>
       <c r="B891" t="s">
-        <v>261</v>
+        <v>227</v>
       </c>
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.25">
@@ -7876,7 +7870,7 @@
         <v>12</v>
       </c>
       <c r="B893" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.25">
@@ -7932,7 +7926,7 @@
         <v>30</v>
       </c>
       <c r="B900" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.25">
@@ -7969,7 +7963,7 @@
     </row>
     <row r="906" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A906" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B906" s="1"/>
     </row>
@@ -8016,7 +8010,7 @@
         <v>8</v>
       </c>
       <c r="B912" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.25">
@@ -8024,7 +8018,7 @@
         <v>10</v>
       </c>
       <c r="B913" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.25">
@@ -8088,7 +8082,7 @@
         <v>32</v>
       </c>
       <c r="B921" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.25">
@@ -8096,7 +8090,7 @@
         <v>58</v>
       </c>
       <c r="B922" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.25">
@@ -8112,7 +8106,7 @@
         <v>81</v>
       </c>
       <c r="B924" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.25">
@@ -8125,7 +8119,7 @@
     </row>
     <row r="927" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A927" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B927" s="1"/>
     </row>
@@ -8284,7 +8278,7 @@
         <v>81</v>
       </c>
       <c r="B947" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.25">
@@ -8292,12 +8286,12 @@
         <v>83</v>
       </c>
       <c r="B948" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="950" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A950" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B950" s="1"/>
     </row>
@@ -8456,7 +8450,7 @@
         <v>81</v>
       </c>
       <c r="B970" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.25">
@@ -8469,7 +8463,7 @@
     </row>
     <row r="973" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A973" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B973" s="1"/>
     </row>
@@ -8508,7 +8502,7 @@
         <v>8</v>
       </c>
       <c r="B978" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.25">
@@ -8716,15 +8710,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>7</v>
@@ -8732,7 +8726,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -8740,7 +8734,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -8748,7 +8742,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -8756,7 +8750,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -8764,7 +8758,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>246</v>
+        <v>146</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -8772,7 +8766,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -8780,7 +8774,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -8876,7 +8870,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B21">
         <v>7</v>
@@ -8884,7 +8878,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B22">
         <v>7</v>
@@ -8900,7 +8894,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24">
         <v>7</v>
@@ -8908,7 +8902,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="B25">
         <v>7</v>
@@ -8916,7 +8910,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>209</v>
       </c>
       <c r="B26">
         <v>7</v>
@@ -8924,7 +8918,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="B27">
         <v>7</v>
@@ -8932,7 +8926,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B28">
         <v>7</v>
@@ -8940,7 +8934,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -8948,7 +8942,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B30">
         <v>7</v>
@@ -8956,7 +8950,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B31">
         <v>7</v>
@@ -8964,7 +8958,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32">
         <v>7</v>
@@ -8972,7 +8966,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33">
         <v>7</v>
@@ -8980,7 +8974,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B34">
         <v>7</v>
@@ -8988,7 +8982,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -8996,7 +8990,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B36">
         <v>7</v>
@@ -9004,7 +8998,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B37">
         <v>7</v>
@@ -9012,7 +9006,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="B38">
         <v>7</v>
@@ -9020,7 +9014,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B39">
         <v>7</v>
@@ -9028,7 +9022,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="B40">
         <v>7</v>
@@ -9036,7 +9030,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B41">
         <v>7</v>
@@ -9044,7 +9038,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B42">
         <v>7</v>
@@ -9052,7 +9046,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B43">
         <v>7</v>

--- a/src/outputs/ss-end-sem-ta_schedule-final.xlsx
+++ b/src/outputs/ss-end-sem-ta_schedule-final.xlsx
@@ -3,20 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88311EA-F9DA-4C3A-BD6D-B3F78A0F4ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22250949-CD3F-4F3C-9893-BC933F05CCCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TA Schedule" sheetId="1" r:id="rId1"/>
     <sheet name="Sessions Count" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="274">
   <si>
     <t>Room</t>
   </si>
@@ -180,9 +180,6 @@
     <t>Florence Koomson</t>
   </si>
   <si>
-    <t>Solomon Akumanyin</t>
-  </si>
-  <si>
     <t>VCR</t>
   </si>
   <si>
@@ -759,9 +756,6 @@
     <t>Jemimah Nyarkoa / Henry Tutu Adjei</t>
   </si>
   <si>
-    <t>Godfred Adu Mensah / Nartey Lamech Narte</t>
-  </si>
-  <si>
     <t>Tuesday, 1 September 2026</t>
   </si>
   <si>
@@ -823,6 +817,27 @@
   </si>
   <si>
     <t>Total Sessions</t>
+  </si>
+  <si>
+    <t>Divine Adjabeng Jnr</t>
+  </si>
+  <si>
+    <t>Divine Adjabeng Jnr / Karis Richardson</t>
+  </si>
+  <si>
+    <t>Livingstone Ayivor</t>
+  </si>
+  <si>
+    <t>Livingstone Ayivor / Augustine Gyening</t>
+  </si>
+  <si>
+    <t>Godfred Adu Mensah / Livingstone Ayivor</t>
+  </si>
+  <si>
+    <t>Nana Ampofo Kusi-Mensah / Livingstone Ayivor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Nyamador </t>
   </si>
 </sst>
 </file>
@@ -878,8 +893,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1235,16 +1250,16 @@
       </c>
     </row>
     <row r="2" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="3" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1399,16 +1414,16 @@
       </c>
     </row>
     <row r="24" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="4"/>
+      <c r="B24" s="5"/>
     </row>
     <row r="25" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="4"/>
     </row>
     <row r="26" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
@@ -1527,15 +1542,15 @@
         <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" t="s">
         <v>55</v>
-      </c>
-      <c r="B41" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -1543,15 +1558,15 @@
         <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
         <v>58</v>
-      </c>
-      <c r="B43" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
@@ -1559,7 +1574,7 @@
         <v>34</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
@@ -1567,20 +1582,20 @@
         <v>36</v>
       </c>
       <c r="B45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" s="5"/>
+    </row>
+    <row r="48" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A47" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B47" s="4"/>
-    </row>
-    <row r="48" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="5"/>
+      <c r="B48" s="4"/>
     </row>
     <row r="49" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
@@ -1595,7 +1610,7 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
@@ -1603,7 +1618,7 @@
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
@@ -1611,7 +1626,7 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -1619,7 +1634,7 @@
         <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -1627,7 +1642,7 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
@@ -1635,7 +1650,7 @@
         <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
@@ -1643,7 +1658,7 @@
         <v>18</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
@@ -1651,7 +1666,7 @@
         <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
@@ -1659,7 +1674,7 @@
         <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -1667,7 +1682,7 @@
         <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -1675,7 +1690,7 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -1683,15 +1698,15 @@
         <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
@@ -1699,15 +1714,15 @@
         <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -1715,7 +1730,7 @@
         <v>34</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
@@ -1723,7 +1738,7 @@
         <v>36</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -1731,36 +1746,36 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" t="s">
         <v>81</v>
-      </c>
-      <c r="B68" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" t="s">
         <v>83</v>
       </c>
-      <c r="B69" t="s">
+    </row>
+    <row r="71" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A71" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A71" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B71" s="4"/>
+      <c r="B71" s="5"/>
     </row>
     <row r="72" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B72" s="5"/>
+      <c r="B72" s="4"/>
     </row>
     <row r="73" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
@@ -1775,7 +1790,7 @@
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
@@ -1783,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -1791,7 +1806,7 @@
         <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -1799,7 +1814,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -1807,7 +1822,7 @@
         <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
@@ -1815,7 +1830,7 @@
         <v>18</v>
       </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -1823,7 +1838,7 @@
         <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -1831,7 +1846,7 @@
         <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -1839,7 +1854,7 @@
         <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -1847,7 +1862,7 @@
         <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -1855,15 +1870,15 @@
         <v>32</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -1871,7 +1886,7 @@
         <v>34</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -1879,7 +1894,7 @@
         <v>36</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -1887,28 +1902,28 @@
         <v>38</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A91" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B91" s="4"/>
+      <c r="A91" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B91" s="5"/>
     </row>
     <row r="92" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B92" s="5"/>
+      <c r="B92" s="4"/>
     </row>
     <row r="93" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
@@ -1923,7 +1938,7 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -1931,7 +1946,7 @@
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -1939,7 +1954,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>104</v>
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -1947,7 +1962,7 @@
         <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -1955,7 +1970,7 @@
         <v>18</v>
       </c>
       <c r="B98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -1963,7 +1978,7 @@
         <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -1971,7 +1986,7 @@
         <v>22</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -1979,7 +1994,7 @@
         <v>24</v>
       </c>
       <c r="B101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -1987,7 +2002,7 @@
         <v>26</v>
       </c>
       <c r="B102" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -1995,7 +2010,7 @@
         <v>30</v>
       </c>
       <c r="B103" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -2003,15 +2018,15 @@
         <v>32</v>
       </c>
       <c r="B104" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B105" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -2019,7 +2034,7 @@
         <v>34</v>
       </c>
       <c r="B106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -2027,7 +2042,7 @@
         <v>36</v>
       </c>
       <c r="B107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -2035,20 +2050,20 @@
         <v>38</v>
       </c>
       <c r="B108" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="110" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A110" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B110" s="4"/>
+      <c r="A110" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B110" s="5"/>
     </row>
     <row r="111" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A111" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B111" s="5"/>
+      <c r="A111" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B111" s="4"/>
     </row>
     <row r="112" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
@@ -2063,7 +2078,7 @@
         <v>4</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -2071,7 +2086,7 @@
         <v>6</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -2079,7 +2094,7 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -2087,7 +2102,7 @@
         <v>10</v>
       </c>
       <c r="B116" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -2095,7 +2110,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -2103,7 +2118,7 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -2111,7 +2126,7 @@
         <v>16</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -2119,7 +2134,7 @@
         <v>18</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -2127,7 +2142,7 @@
         <v>20</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -2135,7 +2150,7 @@
         <v>22</v>
       </c>
       <c r="B122" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -2143,7 +2158,7 @@
         <v>24</v>
       </c>
       <c r="B123" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -2151,7 +2166,7 @@
         <v>26</v>
       </c>
       <c r="B124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -2159,7 +2174,7 @@
         <v>28</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -2167,7 +2182,7 @@
         <v>30</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -2175,15 +2190,15 @@
         <v>32</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -2191,7 +2206,7 @@
         <v>34</v>
       </c>
       <c r="B129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -2199,36 +2214,36 @@
         <v>36</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B132" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A134" s="5" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A134" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B134" s="4"/>
+      <c r="B134" s="5"/>
     </row>
     <row r="135" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A135" s="5" t="s">
+      <c r="A135" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B135" s="5"/>
+      <c r="B135" s="4"/>
     </row>
     <row r="136" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
@@ -2259,7 +2274,7 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -2267,7 +2282,7 @@
         <v>10</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -2275,7 +2290,7 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -2283,7 +2298,7 @@
         <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -2291,7 +2306,7 @@
         <v>16</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -2307,7 +2322,7 @@
         <v>20</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -2315,7 +2330,7 @@
         <v>22</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -2323,7 +2338,7 @@
         <v>24</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -2347,15 +2362,15 @@
         <v>30</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B151" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -2363,15 +2378,15 @@
         <v>32</v>
       </c>
       <c r="B152" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B153" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -2379,7 +2394,7 @@
         <v>34</v>
       </c>
       <c r="B154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -2400,31 +2415,31 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B157" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B158" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A160" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B160" s="4"/>
+      <c r="A160" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B160" s="5"/>
     </row>
     <row r="161" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A161" s="5" t="s">
+      <c r="A161" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B161" s="5"/>
+      <c r="B161" s="4"/>
     </row>
     <row r="162" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3" t="s">
@@ -2439,7 +2454,7 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -2460,7 +2475,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B166" t="s">
         <v>27</v>
@@ -2468,7 +2483,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B167" t="s">
         <v>29</v>
@@ -2503,7 +2518,7 @@
         <v>22</v>
       </c>
       <c r="B171" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -2511,7 +2526,7 @@
         <v>24</v>
       </c>
       <c r="B172" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -2527,7 +2542,7 @@
         <v>28</v>
       </c>
       <c r="B174" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -2535,7 +2550,7 @@
         <v>30</v>
       </c>
       <c r="B175" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -2548,7 +2563,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B177" t="s">
         <v>33</v>
@@ -2580,31 +2595,31 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B181" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B182" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="184" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A184" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B184" s="4"/>
+      <c r="A184" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B184" s="5"/>
     </row>
     <row r="185" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A185" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B185" s="5"/>
+      <c r="A185" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B185" s="4"/>
     </row>
     <row r="186" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
@@ -2619,7 +2634,7 @@
         <v>4</v>
       </c>
       <c r="B187" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -2627,7 +2642,7 @@
         <v>6</v>
       </c>
       <c r="B188" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -2635,7 +2650,7 @@
         <v>8</v>
       </c>
       <c r="B189" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -2643,7 +2658,7 @@
         <v>10</v>
       </c>
       <c r="B190" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -2651,7 +2666,7 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -2659,7 +2674,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -2667,7 +2682,7 @@
         <v>18</v>
       </c>
       <c r="B193" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -2675,7 +2690,7 @@
         <v>20</v>
       </c>
       <c r="B194" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -2683,7 +2698,7 @@
         <v>22</v>
       </c>
       <c r="B195" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -2691,7 +2706,7 @@
         <v>24</v>
       </c>
       <c r="B196" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -2699,7 +2714,7 @@
         <v>26</v>
       </c>
       <c r="B197" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -2707,7 +2722,7 @@
         <v>28</v>
       </c>
       <c r="B198" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -2715,7 +2730,7 @@
         <v>30</v>
       </c>
       <c r="B199" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -2723,7 +2738,7 @@
         <v>32</v>
       </c>
       <c r="B200" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -2731,7 +2746,7 @@
         <v>34</v>
       </c>
       <c r="B201" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -2739,7 +2754,7 @@
         <v>36</v>
       </c>
       <c r="B202" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -2747,36 +2762,36 @@
         <v>38</v>
       </c>
       <c r="B203" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B204" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B205" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A207" s="5" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="207" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A207" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B207" s="4"/>
+      <c r="B207" s="5"/>
     </row>
     <row r="208" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A208" s="5" t="s">
+      <c r="A208" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B208" s="5"/>
+      <c r="B208" s="4"/>
     </row>
     <row r="209" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
@@ -2791,7 +2806,7 @@
         <v>4</v>
       </c>
       <c r="B210" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -2799,7 +2814,7 @@
         <v>6</v>
       </c>
       <c r="B211" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -2807,7 +2822,7 @@
         <v>8</v>
       </c>
       <c r="B212" t="s">
-        <v>88</v>
+        <v>268</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -2815,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="B213" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -2823,7 +2838,7 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -2831,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -2839,7 +2854,7 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -2847,7 +2862,7 @@
         <v>20</v>
       </c>
       <c r="B217" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -2855,7 +2870,7 @@
         <v>22</v>
       </c>
       <c r="B218" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -2863,7 +2878,7 @@
         <v>24</v>
       </c>
       <c r="B219" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -2871,7 +2886,7 @@
         <v>26</v>
       </c>
       <c r="B220" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -2879,7 +2894,7 @@
         <v>30</v>
       </c>
       <c r="B221" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -2887,15 +2902,15 @@
         <v>32</v>
       </c>
       <c r="B222" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B223" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -2903,7 +2918,7 @@
         <v>34</v>
       </c>
       <c r="B224" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -2911,7 +2926,7 @@
         <v>36</v>
       </c>
       <c r="B225" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -2919,28 +2934,28 @@
         <v>38</v>
       </c>
       <c r="B226" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B227" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="229" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A229" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B229" s="4"/>
+      <c r="A229" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B229" s="5"/>
     </row>
     <row r="230" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A230" s="5" t="s">
+      <c r="A230" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B230" s="5"/>
+      <c r="B230" s="4"/>
     </row>
     <row r="231" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
@@ -2955,7 +2970,7 @@
         <v>4</v>
       </c>
       <c r="B232" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -2963,7 +2978,7 @@
         <v>6</v>
       </c>
       <c r="B233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -2971,7 +2986,7 @@
         <v>8</v>
       </c>
       <c r="B234" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -2979,7 +2994,7 @@
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -2987,7 +3002,7 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -2995,7 +3010,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -3003,7 +3018,7 @@
         <v>18</v>
       </c>
       <c r="B238" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -3011,7 +3026,7 @@
         <v>20</v>
       </c>
       <c r="B239" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -3019,7 +3034,7 @@
         <v>22</v>
       </c>
       <c r="B240" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -3027,7 +3042,7 @@
         <v>24</v>
       </c>
       <c r="B241" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -3035,7 +3050,7 @@
         <v>26</v>
       </c>
       <c r="B242" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -3043,7 +3058,7 @@
         <v>28</v>
       </c>
       <c r="B243" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -3051,7 +3066,7 @@
         <v>30</v>
       </c>
       <c r="B244" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -3059,15 +3074,15 @@
         <v>32</v>
       </c>
       <c r="B245" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B246" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -3075,7 +3090,7 @@
         <v>34</v>
       </c>
       <c r="B247" t="s">
-        <v>177</v>
+        <v>270</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -3083,7 +3098,7 @@
         <v>36</v>
       </c>
       <c r="B248" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -3091,20 +3106,20 @@
         <v>38</v>
       </c>
       <c r="B249" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="251" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A251" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B251" s="4"/>
+      <c r="A251" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B251" s="5"/>
     </row>
     <row r="252" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A252" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B252" s="5"/>
+      <c r="A252" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B252" s="4"/>
     </row>
     <row r="253" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3" t="s">
@@ -3119,7 +3134,7 @@
         <v>4</v>
       </c>
       <c r="B254" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -3127,7 +3142,7 @@
         <v>8</v>
       </c>
       <c r="B255" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -3135,7 +3150,7 @@
         <v>10</v>
       </c>
       <c r="B256" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -3143,7 +3158,7 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -3151,7 +3166,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -3159,7 +3174,7 @@
         <v>18</v>
       </c>
       <c r="B259" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -3167,7 +3182,7 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -3175,7 +3190,7 @@
         <v>22</v>
       </c>
       <c r="B261" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -3183,7 +3198,7 @@
         <v>24</v>
       </c>
       <c r="B262" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -3191,7 +3206,7 @@
         <v>26</v>
       </c>
       <c r="B263" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -3199,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="B264" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -3207,15 +3222,15 @@
         <v>32</v>
       </c>
       <c r="B265" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B266" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -3223,7 +3238,7 @@
         <v>34</v>
       </c>
       <c r="B267" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -3231,7 +3246,7 @@
         <v>36</v>
       </c>
       <c r="B268" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -3239,20 +3254,20 @@
         <v>38</v>
       </c>
       <c r="B269" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="271" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A271" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B271" s="4"/>
+      <c r="A271" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B271" s="5"/>
     </row>
     <row r="272" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A272" s="5" t="s">
+      <c r="A272" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B272" s="5"/>
+      <c r="B272" s="4"/>
     </row>
     <row r="273" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3" t="s">
@@ -3267,7 +3282,7 @@
         <v>4</v>
       </c>
       <c r="B274" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -3275,7 +3290,7 @@
         <v>8</v>
       </c>
       <c r="B275" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -3283,7 +3298,7 @@
         <v>10</v>
       </c>
       <c r="B276" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -3291,7 +3306,7 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -3299,7 +3314,7 @@
         <v>16</v>
       </c>
       <c r="B278" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -3307,7 +3322,7 @@
         <v>18</v>
       </c>
       <c r="B279" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -3315,7 +3330,7 @@
         <v>20</v>
       </c>
       <c r="B280" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -3323,7 +3338,7 @@
         <v>22</v>
       </c>
       <c r="B281" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -3331,7 +3346,7 @@
         <v>24</v>
       </c>
       <c r="B282" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -3339,7 +3354,7 @@
         <v>26</v>
       </c>
       <c r="B283" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -3347,15 +3362,15 @@
         <v>30</v>
       </c>
       <c r="B284" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B285" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -3363,7 +3378,7 @@
         <v>32</v>
       </c>
       <c r="B286" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -3371,7 +3386,7 @@
         <v>34</v>
       </c>
       <c r="B287" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -3379,7 +3394,7 @@
         <v>36</v>
       </c>
       <c r="B288" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -3392,31 +3407,31 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B290" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B291" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="293" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A293" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B293" s="4"/>
+      <c r="A293" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B293" s="5"/>
     </row>
     <row r="294" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A294" s="5" t="s">
+      <c r="A294" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B294" s="5"/>
+      <c r="B294" s="4"/>
     </row>
     <row r="295" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
@@ -3428,7 +3443,7 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B296" t="s">
         <v>31</v>
@@ -3455,7 +3470,7 @@
         <v>8</v>
       </c>
       <c r="B299" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -3479,7 +3494,7 @@
         <v>14</v>
       </c>
       <c r="B302" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -3487,7 +3502,7 @@
         <v>16</v>
       </c>
       <c r="B303" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -3548,10 +3563,10 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B311" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -3559,20 +3574,20 @@
         <v>34</v>
       </c>
       <c r="B312" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="314" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A314" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B314" s="4"/>
+      <c r="A314" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B314" s="5"/>
     </row>
     <row r="315" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A315" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B315" s="5"/>
+      <c r="A315" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B315" s="4"/>
     </row>
     <row r="316" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
@@ -3584,7 +3599,7 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B317" t="s">
         <v>42</v>
@@ -3603,7 +3618,7 @@
         <v>6</v>
       </c>
       <c r="B319" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
@@ -3611,7 +3626,7 @@
         <v>8</v>
       </c>
       <c r="B320" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
@@ -3627,7 +3642,7 @@
         <v>12</v>
       </c>
       <c r="B322" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -3635,12 +3650,12 @@
         <v>14</v>
       </c>
       <c r="B323" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B324" t="s">
         <v>41</v>
@@ -3648,10 +3663,10 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B325" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -3691,7 +3706,7 @@
         <v>24</v>
       </c>
       <c r="B330" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -3707,7 +3722,7 @@
         <v>28</v>
       </c>
       <c r="B332" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -3720,10 +3735,10 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B334" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
@@ -3731,15 +3746,15 @@
         <v>32</v>
       </c>
       <c r="B335" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
+        <v>57</v>
+      </c>
+      <c r="B336" t="s">
         <v>58</v>
-      </c>
-      <c r="B336" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
@@ -3747,7 +3762,7 @@
         <v>34</v>
       </c>
       <c r="B337" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
@@ -3755,7 +3770,7 @@
         <v>36</v>
       </c>
       <c r="B338" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
@@ -3763,36 +3778,36 @@
         <v>38</v>
       </c>
       <c r="B339" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B340" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B341" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A343" s="5" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="343" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A343" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B343" s="4"/>
+      <c r="B343" s="5"/>
     </row>
     <row r="344" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A344" s="5" t="s">
+      <c r="A344" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B344" s="5"/>
+      <c r="B344" s="4"/>
     </row>
     <row r="345" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
@@ -3804,10 +3819,10 @@
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B346" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
@@ -3815,7 +3830,7 @@
         <v>8</v>
       </c>
       <c r="B347" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
@@ -3823,7 +3838,7 @@
         <v>10</v>
       </c>
       <c r="B348" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
@@ -3831,7 +3846,7 @@
         <v>12</v>
       </c>
       <c r="B349" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
@@ -3839,7 +3854,7 @@
         <v>14</v>
       </c>
       <c r="B350" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
@@ -3847,7 +3862,7 @@
         <v>16</v>
       </c>
       <c r="B351" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
@@ -3855,7 +3870,7 @@
         <v>18</v>
       </c>
       <c r="B352" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
@@ -3863,7 +3878,7 @@
         <v>20</v>
       </c>
       <c r="B353" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
@@ -3871,7 +3886,7 @@
         <v>22</v>
       </c>
       <c r="B354" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
@@ -3879,15 +3894,15 @@
         <v>24</v>
       </c>
       <c r="B355" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B356" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
@@ -3895,15 +3910,15 @@
         <v>32</v>
       </c>
       <c r="B357" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B358" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
@@ -3911,7 +3926,7 @@
         <v>34</v>
       </c>
       <c r="B359" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
@@ -3919,36 +3934,36 @@
         <v>36</v>
       </c>
       <c r="B360" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B361" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B362" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="364" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A364" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B364" s="4"/>
+      <c r="A364" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B364" s="5"/>
     </row>
     <row r="365" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A365" s="5" t="s">
+      <c r="A365" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B365" s="5"/>
+      <c r="B365" s="4"/>
     </row>
     <row r="366" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
@@ -3960,10 +3975,10 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B367" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
@@ -3971,7 +3986,7 @@
         <v>4</v>
       </c>
       <c r="B368" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
@@ -3979,7 +3994,7 @@
         <v>6</v>
       </c>
       <c r="B369" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
@@ -3987,7 +4002,7 @@
         <v>8</v>
       </c>
       <c r="B370" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
@@ -3995,7 +4010,7 @@
         <v>12</v>
       </c>
       <c r="B371" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
@@ -4003,7 +4018,7 @@
         <v>16</v>
       </c>
       <c r="B372" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
@@ -4011,7 +4026,7 @@
         <v>18</v>
       </c>
       <c r="B373" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
@@ -4019,7 +4034,7 @@
         <v>20</v>
       </c>
       <c r="B374" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
@@ -4027,7 +4042,7 @@
         <v>22</v>
       </c>
       <c r="B375" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
@@ -4035,15 +4050,15 @@
         <v>24</v>
       </c>
       <c r="B376" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B377" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
@@ -4051,7 +4066,7 @@
         <v>32</v>
       </c>
       <c r="B378" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
@@ -4059,7 +4074,7 @@
         <v>34</v>
       </c>
       <c r="B379" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
@@ -4067,7 +4082,7 @@
         <v>36</v>
       </c>
       <c r="B380" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
@@ -4075,20 +4090,20 @@
         <v>38</v>
       </c>
       <c r="B381" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="383" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A383" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B383" s="4"/>
+      <c r="A383" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B383" s="5"/>
     </row>
     <row r="384" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A384" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B384" s="5"/>
+      <c r="A384" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B384" s="4"/>
     </row>
     <row r="385" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
@@ -4100,10 +4115,10 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B386" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
@@ -4111,7 +4126,7 @@
         <v>4</v>
       </c>
       <c r="B387" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
@@ -4119,7 +4134,7 @@
         <v>6</v>
       </c>
       <c r="B388" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
@@ -4127,7 +4142,7 @@
         <v>8</v>
       </c>
       <c r="B389" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
@@ -4135,7 +4150,7 @@
         <v>12</v>
       </c>
       <c r="B390" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
@@ -4143,7 +4158,7 @@
         <v>16</v>
       </c>
       <c r="B391" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
@@ -4151,7 +4166,7 @@
         <v>18</v>
       </c>
       <c r="B392" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
@@ -4159,7 +4174,7 @@
         <v>20</v>
       </c>
       <c r="B393" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
@@ -4167,7 +4182,7 @@
         <v>22</v>
       </c>
       <c r="B394" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
@@ -4175,7 +4190,7 @@
         <v>24</v>
       </c>
       <c r="B395" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
@@ -4183,7 +4198,7 @@
         <v>26</v>
       </c>
       <c r="B396" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
@@ -4191,7 +4206,7 @@
         <v>28</v>
       </c>
       <c r="B397" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
@@ -4199,7 +4214,7 @@
         <v>30</v>
       </c>
       <c r="B398" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
@@ -4207,15 +4222,15 @@
         <v>32</v>
       </c>
       <c r="B399" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B400" t="s">
-        <v>113</v>
+        <v>269</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
@@ -4223,7 +4238,7 @@
         <v>34</v>
       </c>
       <c r="B401" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
@@ -4231,7 +4246,7 @@
         <v>36</v>
       </c>
       <c r="B402" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
@@ -4239,20 +4254,20 @@
         <v>38</v>
       </c>
       <c r="B403" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="405" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A405" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B405" s="4"/>
+      <c r="A405" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B405" s="5"/>
     </row>
     <row r="406" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A406" s="5" t="s">
+      <c r="A406" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B406" s="5"/>
+      <c r="B406" s="4"/>
     </row>
     <row r="407" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3" t="s">
@@ -4264,10 +4279,10 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B408" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
@@ -4275,7 +4290,7 @@
         <v>4</v>
       </c>
       <c r="B409" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
@@ -4283,7 +4298,7 @@
         <v>6</v>
       </c>
       <c r="B410" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
@@ -4291,7 +4306,7 @@
         <v>8</v>
       </c>
       <c r="B411" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
@@ -4299,7 +4314,7 @@
         <v>12</v>
       </c>
       <c r="B412" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
@@ -4307,7 +4322,7 @@
         <v>14</v>
       </c>
       <c r="B413" t="s">
-        <v>182</v>
+        <v>267</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
@@ -4315,7 +4330,7 @@
         <v>16</v>
       </c>
       <c r="B414" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
@@ -4323,7 +4338,7 @@
         <v>18</v>
       </c>
       <c r="B415" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
@@ -4331,7 +4346,7 @@
         <v>20</v>
       </c>
       <c r="B416" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
@@ -4339,7 +4354,7 @@
         <v>22</v>
       </c>
       <c r="B417" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
@@ -4347,7 +4362,7 @@
         <v>24</v>
       </c>
       <c r="B418" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
@@ -4355,7 +4370,7 @@
         <v>26</v>
       </c>
       <c r="B419" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
@@ -4363,7 +4378,7 @@
         <v>28</v>
       </c>
       <c r="B420" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
@@ -4371,15 +4386,15 @@
         <v>30</v>
       </c>
       <c r="B421" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B422" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
@@ -4387,7 +4402,7 @@
         <v>32</v>
       </c>
       <c r="B423" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
@@ -4395,7 +4410,7 @@
         <v>34</v>
       </c>
       <c r="B424" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
@@ -4403,7 +4418,7 @@
         <v>36</v>
       </c>
       <c r="B425" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
@@ -4411,28 +4426,28 @@
         <v>38</v>
       </c>
       <c r="B426" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B427" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="429" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A429" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B429" s="4"/>
+      <c r="A429" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B429" s="5"/>
     </row>
     <row r="430" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A430" s="5" t="s">
+      <c r="A430" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B430" s="5"/>
+      <c r="B430" s="4"/>
     </row>
     <row r="431" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
@@ -4444,7 +4459,7 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B432" t="s">
         <v>5</v>
@@ -4455,7 +4470,7 @@
         <v>4</v>
       </c>
       <c r="B433" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
@@ -4479,7 +4494,7 @@
         <v>12</v>
       </c>
       <c r="B436" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
@@ -4495,7 +4510,7 @@
         <v>18</v>
       </c>
       <c r="B438" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
@@ -4503,7 +4518,7 @@
         <v>20</v>
       </c>
       <c r="B439" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
@@ -4511,7 +4526,7 @@
         <v>22</v>
       </c>
       <c r="B440" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
@@ -4548,7 +4563,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B445" t="s">
         <v>13</v>
@@ -4559,7 +4574,7 @@
         <v>34</v>
       </c>
       <c r="B446" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
@@ -4567,7 +4582,7 @@
         <v>36</v>
       </c>
       <c r="B447" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
@@ -4575,20 +4590,20 @@
         <v>38</v>
       </c>
       <c r="B448" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="450" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A450" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B450" s="4"/>
+      <c r="A450" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B450" s="5"/>
     </row>
     <row r="451" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A451" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B451" s="5"/>
+      <c r="A451" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B451" s="4"/>
     </row>
     <row r="452" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A452" s="3" t="s">
@@ -4600,10 +4615,10 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B453" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
@@ -4611,7 +4626,7 @@
         <v>4</v>
       </c>
       <c r="B454" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
@@ -4627,7 +4642,7 @@
         <v>8</v>
       </c>
       <c r="B456" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
@@ -4651,7 +4666,7 @@
         <v>18</v>
       </c>
       <c r="B459" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
@@ -4683,7 +4698,7 @@
         <v>30</v>
       </c>
       <c r="B463" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
@@ -4696,7 +4711,7 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B465" t="s">
         <v>50</v>
@@ -4707,7 +4722,7 @@
         <v>34</v>
       </c>
       <c r="B466" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
@@ -4723,20 +4738,20 @@
         <v>38</v>
       </c>
       <c r="B468" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="470" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A470" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B470" s="4"/>
+      <c r="A470" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B470" s="5"/>
     </row>
     <row r="471" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A471" s="5" t="s">
+      <c r="A471" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B471" s="5"/>
+      <c r="B471" s="4"/>
     </row>
     <row r="472" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A472" s="3" t="s">
@@ -4748,7 +4763,7 @@
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B473" t="s">
         <v>53</v>
@@ -4759,7 +4774,7 @@
         <v>8</v>
       </c>
       <c r="B474" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
@@ -4775,7 +4790,7 @@
         <v>14</v>
       </c>
       <c r="B476" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
@@ -4783,7 +4798,7 @@
         <v>16</v>
       </c>
       <c r="B477" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
@@ -4791,7 +4806,7 @@
         <v>18</v>
       </c>
       <c r="B478" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
@@ -4799,7 +4814,7 @@
         <v>20</v>
       </c>
       <c r="B479" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
@@ -4807,7 +4822,7 @@
         <v>22</v>
       </c>
       <c r="B480" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
@@ -4815,7 +4830,7 @@
         <v>24</v>
       </c>
       <c r="B481" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
@@ -4823,7 +4838,7 @@
         <v>30</v>
       </c>
       <c r="B482" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
@@ -4831,15 +4846,15 @@
         <v>32</v>
       </c>
       <c r="B483" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B484" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
@@ -4847,7 +4862,7 @@
         <v>34</v>
       </c>
       <c r="B485" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
@@ -4855,7 +4870,7 @@
         <v>36</v>
       </c>
       <c r="B486" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
@@ -4863,20 +4878,20 @@
         <v>38</v>
       </c>
       <c r="B487" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="489" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A489" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B489" s="4"/>
+      <c r="A489" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B489" s="5"/>
     </row>
     <row r="490" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A490" s="5" t="s">
+      <c r="A490" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B490" s="5"/>
+      <c r="B490" s="4"/>
     </row>
     <row r="491" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3" t="s">
@@ -4888,10 +4903,10 @@
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B492" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
@@ -4899,7 +4914,7 @@
         <v>8</v>
       </c>
       <c r="B493" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
@@ -4907,7 +4922,7 @@
         <v>12</v>
       </c>
       <c r="B494" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
@@ -4915,7 +4930,7 @@
         <v>16</v>
       </c>
       <c r="B495" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
@@ -4923,7 +4938,7 @@
         <v>18</v>
       </c>
       <c r="B496" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
@@ -4931,7 +4946,7 @@
         <v>20</v>
       </c>
       <c r="B497" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
@@ -4939,7 +4954,7 @@
         <v>22</v>
       </c>
       <c r="B498" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
@@ -4947,7 +4962,7 @@
         <v>24</v>
       </c>
       <c r="B499" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
@@ -4955,7 +4970,7 @@
         <v>26</v>
       </c>
       <c r="B500" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
@@ -4963,7 +4978,7 @@
         <v>28</v>
       </c>
       <c r="B501" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
@@ -4971,7 +4986,7 @@
         <v>30</v>
       </c>
       <c r="B502" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
@@ -4979,15 +4994,15 @@
         <v>32</v>
       </c>
       <c r="B503" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B504" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
@@ -4995,36 +5010,36 @@
         <v>34</v>
       </c>
       <c r="B505" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
+        <v>80</v>
+      </c>
+      <c r="B506" t="s">
         <v>81</v>
-      </c>
-      <c r="B506" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
+        <v>82</v>
+      </c>
+      <c r="B507" t="s">
         <v>83</v>
       </c>
-      <c r="B507" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="509" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A509" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B509" s="4"/>
+      <c r="A509" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B509" s="5"/>
     </row>
     <row r="510" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A510" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B510" s="5"/>
+      <c r="A510" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B510" s="4"/>
     </row>
     <row r="511" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3" t="s">
@@ -5036,10 +5051,10 @@
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B512" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
@@ -5047,7 +5062,7 @@
         <v>4</v>
       </c>
       <c r="B513" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
@@ -5055,7 +5070,7 @@
         <v>8</v>
       </c>
       <c r="B514" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
@@ -5063,7 +5078,7 @@
         <v>12</v>
       </c>
       <c r="B515" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
@@ -5071,7 +5086,7 @@
         <v>16</v>
       </c>
       <c r="B516" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
@@ -5079,7 +5094,7 @@
         <v>18</v>
       </c>
       <c r="B517" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
@@ -5087,7 +5102,7 @@
         <v>20</v>
       </c>
       <c r="B518" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
@@ -5095,7 +5110,7 @@
         <v>22</v>
       </c>
       <c r="B519" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
@@ -5103,7 +5118,7 @@
         <v>24</v>
       </c>
       <c r="B520" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
@@ -5111,7 +5126,7 @@
         <v>26</v>
       </c>
       <c r="B521" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
@@ -5119,7 +5134,7 @@
         <v>30</v>
       </c>
       <c r="B522" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
@@ -5127,15 +5142,15 @@
         <v>32</v>
       </c>
       <c r="B523" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B524" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
@@ -5143,7 +5158,7 @@
         <v>34</v>
       </c>
       <c r="B525" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
@@ -5151,7 +5166,7 @@
         <v>36</v>
       </c>
       <c r="B526" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
@@ -5159,20 +5174,20 @@
         <v>38</v>
       </c>
       <c r="B527" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="529" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A529" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B529" s="4"/>
+      <c r="A529" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B529" s="5"/>
     </row>
     <row r="530" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A530" s="5" t="s">
+      <c r="A530" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B530" s="5"/>
+      <c r="B530" s="4"/>
     </row>
     <row r="531" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A531" s="3" t="s">
@@ -5184,10 +5199,10 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B532" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
@@ -5195,7 +5210,7 @@
         <v>4</v>
       </c>
       <c r="B533" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
@@ -5203,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B534" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
@@ -5211,7 +5226,7 @@
         <v>8</v>
       </c>
       <c r="B535" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
@@ -5219,7 +5234,7 @@
         <v>12</v>
       </c>
       <c r="B536" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
@@ -5227,7 +5242,7 @@
         <v>14</v>
       </c>
       <c r="B537" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
@@ -5235,7 +5250,7 @@
         <v>16</v>
       </c>
       <c r="B538" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
@@ -5243,7 +5258,7 @@
         <v>18</v>
       </c>
       <c r="B539" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
@@ -5251,7 +5266,7 @@
         <v>20</v>
       </c>
       <c r="B540" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
@@ -5259,7 +5274,7 @@
         <v>22</v>
       </c>
       <c r="B541" t="s">
-        <v>178</v>
+        <v>269</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
@@ -5267,7 +5282,7 @@
         <v>24</v>
       </c>
       <c r="B542" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
@@ -5275,7 +5290,7 @@
         <v>26</v>
       </c>
       <c r="B543" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
@@ -5283,7 +5298,7 @@
         <v>30</v>
       </c>
       <c r="B544" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
@@ -5291,15 +5306,15 @@
         <v>32</v>
       </c>
       <c r="B545" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B546" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
@@ -5307,7 +5322,7 @@
         <v>34</v>
       </c>
       <c r="B547" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
@@ -5315,7 +5330,7 @@
         <v>36</v>
       </c>
       <c r="B548" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
@@ -5323,20 +5338,20 @@
         <v>38</v>
       </c>
       <c r="B549" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="551" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A551" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B551" s="4"/>
+      <c r="A551" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B551" s="5"/>
     </row>
     <row r="552" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A552" s="5" t="s">
+      <c r="A552" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B552" s="5"/>
+      <c r="B552" s="4"/>
     </row>
     <row r="553" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A553" s="3" t="s">
@@ -5348,10 +5363,10 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B554" t="s">
-        <v>180</v>
+        <v>267</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
@@ -5359,7 +5374,7 @@
         <v>4</v>
       </c>
       <c r="B555" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
@@ -5367,7 +5382,7 @@
         <v>6</v>
       </c>
       <c r="B556" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
@@ -5375,7 +5390,7 @@
         <v>8</v>
       </c>
       <c r="B557" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
@@ -5383,7 +5398,7 @@
         <v>12</v>
       </c>
       <c r="B558" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
@@ -5391,7 +5406,7 @@
         <v>16</v>
       </c>
       <c r="B559" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
@@ -5399,7 +5414,7 @@
         <v>18</v>
       </c>
       <c r="B560" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
@@ -5407,7 +5422,7 @@
         <v>20</v>
       </c>
       <c r="B561" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
@@ -5415,7 +5430,7 @@
         <v>22</v>
       </c>
       <c r="B562" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
@@ -5423,7 +5438,7 @@
         <v>24</v>
       </c>
       <c r="B563" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
@@ -5431,7 +5446,7 @@
         <v>26</v>
       </c>
       <c r="B564" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
@@ -5439,7 +5454,7 @@
         <v>30</v>
       </c>
       <c r="B565" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
@@ -5447,15 +5462,15 @@
         <v>32</v>
       </c>
       <c r="B566" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B567" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
@@ -5463,7 +5478,7 @@
         <v>34</v>
       </c>
       <c r="B568" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
@@ -5471,7 +5486,7 @@
         <v>36</v>
       </c>
       <c r="B569" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
@@ -5479,36 +5494,36 @@
         <v>38</v>
       </c>
       <c r="B570" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B571" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B572" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="574" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A574" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B574" s="4"/>
+      <c r="A574" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B574" s="5"/>
     </row>
     <row r="575" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A575" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B575" s="5"/>
+      <c r="A575" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B575" s="4"/>
     </row>
     <row r="576" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
@@ -5520,10 +5535,10 @@
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B577" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
@@ -5531,7 +5546,7 @@
         <v>8</v>
       </c>
       <c r="B578" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
@@ -5539,7 +5554,7 @@
         <v>12</v>
       </c>
       <c r="B579" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
@@ -5547,7 +5562,7 @@
         <v>16</v>
       </c>
       <c r="B580" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
@@ -5555,7 +5570,7 @@
         <v>18</v>
       </c>
       <c r="B581" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
@@ -5563,7 +5578,7 @@
         <v>20</v>
       </c>
       <c r="B582" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
@@ -5571,7 +5586,7 @@
         <v>22</v>
       </c>
       <c r="B583" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
@@ -5579,15 +5594,15 @@
         <v>24</v>
       </c>
       <c r="B584" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B585" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
@@ -5595,15 +5610,15 @@
         <v>32</v>
       </c>
       <c r="B586" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B587" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
@@ -5611,7 +5626,7 @@
         <v>34</v>
       </c>
       <c r="B588" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
@@ -5631,16 +5646,16 @@
       </c>
     </row>
     <row r="592" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A592" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B592" s="4"/>
+      <c r="A592" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B592" s="5"/>
     </row>
     <row r="593" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A593" s="5" t="s">
+      <c r="A593" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B593" s="5"/>
+      <c r="B593" s="4"/>
     </row>
     <row r="594" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A594" s="3" t="s">
@@ -5652,7 +5667,7 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B595" t="s">
         <v>29</v>
@@ -5663,7 +5678,7 @@
         <v>4</v>
       </c>
       <c r="B596" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
@@ -5671,7 +5686,7 @@
         <v>6</v>
       </c>
       <c r="B597" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
@@ -5679,7 +5694,7 @@
         <v>8</v>
       </c>
       <c r="B598" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
@@ -5759,15 +5774,15 @@
         <v>32</v>
       </c>
       <c r="B608" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B609" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
@@ -5775,7 +5790,7 @@
         <v>34</v>
       </c>
       <c r="B610" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
@@ -5783,7 +5798,7 @@
         <v>36</v>
       </c>
       <c r="B611" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
@@ -5795,16 +5810,16 @@
       </c>
     </row>
     <row r="614" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A614" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B614" s="4"/>
+      <c r="A614" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B614" s="5"/>
     </row>
     <row r="615" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A615" s="5" t="s">
+      <c r="A615" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B615" s="5"/>
+      <c r="B615" s="4"/>
     </row>
     <row r="616" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A616" s="3" t="s">
@@ -5816,10 +5831,10 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B617" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
@@ -5827,7 +5842,7 @@
         <v>8</v>
       </c>
       <c r="B618" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
@@ -5875,7 +5890,7 @@
         <v>22</v>
       </c>
       <c r="B624" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
@@ -5899,15 +5914,15 @@
         <v>32</v>
       </c>
       <c r="B627" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B628" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
@@ -5915,7 +5930,7 @@
         <v>34</v>
       </c>
       <c r="B629" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
@@ -5923,36 +5938,36 @@
         <v>36</v>
       </c>
       <c r="B630" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B631" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B632" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="634" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A634" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B634" s="4"/>
+      <c r="A634" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B634" s="5"/>
     </row>
     <row r="635" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A635" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B635" s="5"/>
+      <c r="A635" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B635" s="4"/>
     </row>
     <row r="636" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A636" s="3" t="s">
@@ -5964,10 +5979,10 @@
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B637" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
@@ -5975,7 +5990,7 @@
         <v>4</v>
       </c>
       <c r="B638" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
@@ -5983,7 +5998,7 @@
         <v>8</v>
       </c>
       <c r="B639" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
@@ -5991,7 +6006,7 @@
         <v>10</v>
       </c>
       <c r="B640" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
@@ -5999,7 +6014,7 @@
         <v>12</v>
       </c>
       <c r="B641" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
@@ -6007,7 +6022,7 @@
         <v>14</v>
       </c>
       <c r="B642" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
@@ -6015,7 +6030,7 @@
         <v>16</v>
       </c>
       <c r="B643" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
@@ -6023,7 +6038,7 @@
         <v>18</v>
       </c>
       <c r="B644" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
@@ -6031,7 +6046,7 @@
         <v>20</v>
       </c>
       <c r="B645" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
@@ -6039,7 +6054,7 @@
         <v>22</v>
       </c>
       <c r="B646" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
@@ -6047,7 +6062,7 @@
         <v>24</v>
       </c>
       <c r="B647" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
@@ -6055,7 +6070,7 @@
         <v>26</v>
       </c>
       <c r="B648" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
@@ -6063,7 +6078,7 @@
         <v>28</v>
       </c>
       <c r="B649" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
@@ -6071,7 +6086,7 @@
         <v>30</v>
       </c>
       <c r="B650" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
@@ -6079,15 +6094,15 @@
         <v>32</v>
       </c>
       <c r="B651" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B652" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
@@ -6095,7 +6110,7 @@
         <v>34</v>
       </c>
       <c r="B653" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
@@ -6103,7 +6118,7 @@
         <v>36</v>
       </c>
       <c r="B654" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
@@ -6111,20 +6126,20 @@
         <v>38</v>
       </c>
       <c r="B655" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="657" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A657" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B657" s="4"/>
+      <c r="A657" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B657" s="5"/>
     </row>
     <row r="658" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A658" s="5" t="s">
+      <c r="A658" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B658" s="5"/>
+      <c r="B658" s="4"/>
     </row>
     <row r="659" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A659" s="3" t="s">
@@ -6136,10 +6151,10 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B660" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
@@ -6147,7 +6162,7 @@
         <v>4</v>
       </c>
       <c r="B661" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
@@ -6155,7 +6170,7 @@
         <v>6</v>
       </c>
       <c r="B662" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
@@ -6163,7 +6178,7 @@
         <v>8</v>
       </c>
       <c r="B663" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
@@ -6171,7 +6186,7 @@
         <v>10</v>
       </c>
       <c r="B664" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
@@ -6179,7 +6194,7 @@
         <v>12</v>
       </c>
       <c r="B665" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
@@ -6187,7 +6202,7 @@
         <v>16</v>
       </c>
       <c r="B666" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
@@ -6195,7 +6210,7 @@
         <v>18</v>
       </c>
       <c r="B667" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
@@ -6203,7 +6218,7 @@
         <v>20</v>
       </c>
       <c r="B668" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
@@ -6211,7 +6226,7 @@
         <v>22</v>
       </c>
       <c r="B669" t="s">
-        <v>86</v>
+        <v>267</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
@@ -6219,7 +6234,7 @@
         <v>24</v>
       </c>
       <c r="B670" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
@@ -6227,7 +6242,7 @@
         <v>26</v>
       </c>
       <c r="B671" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
@@ -6235,7 +6250,7 @@
         <v>28</v>
       </c>
       <c r="B672" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
@@ -6243,15 +6258,15 @@
         <v>30</v>
       </c>
       <c r="B673" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B674" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
@@ -6259,15 +6274,15 @@
         <v>32</v>
       </c>
       <c r="B675" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B676" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
@@ -6275,7 +6290,7 @@
         <v>34</v>
       </c>
       <c r="B677" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
@@ -6283,7 +6298,7 @@
         <v>36</v>
       </c>
       <c r="B678" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
@@ -6291,36 +6306,36 @@
         <v>38</v>
       </c>
       <c r="B679" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B680" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B681" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="683" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A683" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B683" s="4"/>
+      <c r="A683" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B683" s="5"/>
     </row>
     <row r="684" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A684" s="5" t="s">
+      <c r="A684" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B684" s="5"/>
+      <c r="B684" s="4"/>
     </row>
     <row r="685" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A685" s="3" t="s">
@@ -6332,10 +6347,10 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B686" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
@@ -6343,7 +6358,7 @@
         <v>4</v>
       </c>
       <c r="B687" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
@@ -6351,7 +6366,7 @@
         <v>6</v>
       </c>
       <c r="B688" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
@@ -6359,7 +6374,7 @@
         <v>8</v>
       </c>
       <c r="B689" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
@@ -6367,7 +6382,7 @@
         <v>10</v>
       </c>
       <c r="B690" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
@@ -6375,7 +6390,7 @@
         <v>12</v>
       </c>
       <c r="B691" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
@@ -6383,7 +6398,7 @@
         <v>16</v>
       </c>
       <c r="B692" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
@@ -6391,7 +6406,7 @@
         <v>18</v>
       </c>
       <c r="B693" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
@@ -6399,7 +6414,7 @@
         <v>20</v>
       </c>
       <c r="B694" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
@@ -6407,7 +6422,7 @@
         <v>22</v>
       </c>
       <c r="B695" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
@@ -6415,7 +6430,7 @@
         <v>24</v>
       </c>
       <c r="B696" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
@@ -6423,7 +6438,7 @@
         <v>26</v>
       </c>
       <c r="B697" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
@@ -6431,7 +6446,7 @@
         <v>28</v>
       </c>
       <c r="B698" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
@@ -6439,7 +6454,7 @@
         <v>30</v>
       </c>
       <c r="B699" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
@@ -6447,15 +6462,15 @@
         <v>32</v>
       </c>
       <c r="B700" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B701" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
@@ -6463,7 +6478,7 @@
         <v>34</v>
       </c>
       <c r="B702" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
@@ -6471,36 +6486,36 @@
         <v>38</v>
       </c>
       <c r="B703" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B704" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B705" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
     </row>
     <row r="707" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A707" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B707" s="4"/>
+      <c r="A707" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B707" s="5"/>
     </row>
     <row r="708" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A708" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B708" s="5"/>
+      <c r="A708" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B708" s="4"/>
     </row>
     <row r="709" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A709" s="3" t="s">
@@ -6512,10 +6527,10 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B710" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
@@ -6523,7 +6538,7 @@
         <v>4</v>
       </c>
       <c r="B711" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
@@ -6531,7 +6546,7 @@
         <v>6</v>
       </c>
       <c r="B712" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
@@ -6539,7 +6554,7 @@
         <v>8</v>
       </c>
       <c r="B713" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
@@ -6547,7 +6562,7 @@
         <v>10</v>
       </c>
       <c r="B714" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
@@ -6555,7 +6570,7 @@
         <v>12</v>
       </c>
       <c r="B715" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
@@ -6563,7 +6578,7 @@
         <v>16</v>
       </c>
       <c r="B716" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
@@ -6571,7 +6586,7 @@
         <v>18</v>
       </c>
       <c r="B717" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
@@ -6579,7 +6594,7 @@
         <v>20</v>
       </c>
       <c r="B718" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
@@ -6587,7 +6602,7 @@
         <v>22</v>
       </c>
       <c r="B719" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
@@ -6595,7 +6610,7 @@
         <v>24</v>
       </c>
       <c r="B720" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
@@ -6603,7 +6618,7 @@
         <v>26</v>
       </c>
       <c r="B721" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
@@ -6619,7 +6634,7 @@
         <v>30</v>
       </c>
       <c r="B723" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
@@ -6627,15 +6642,15 @@
         <v>32</v>
       </c>
       <c r="B724" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B725" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
@@ -6643,28 +6658,28 @@
         <v>34</v>
       </c>
       <c r="B726" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B727" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="729" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A729" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B729" s="4"/>
+      <c r="A729" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B729" s="5"/>
     </row>
     <row r="730" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A730" s="5" t="s">
+      <c r="A730" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B730" s="5"/>
+      <c r="B730" s="4"/>
     </row>
     <row r="731" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A731" s="3" t="s">
@@ -6676,7 +6691,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B732" t="s">
         <v>19</v>
@@ -6703,7 +6718,7 @@
         <v>8</v>
       </c>
       <c r="B735" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
@@ -6727,7 +6742,7 @@
         <v>16</v>
       </c>
       <c r="B738" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
@@ -6735,7 +6750,7 @@
         <v>18</v>
       </c>
       <c r="B739" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
@@ -6743,7 +6758,7 @@
         <v>20</v>
       </c>
       <c r="B740" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
@@ -6759,7 +6774,7 @@
         <v>24</v>
       </c>
       <c r="B742" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
@@ -6783,7 +6798,7 @@
         <v>30</v>
       </c>
       <c r="B745" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
@@ -6791,15 +6806,15 @@
         <v>32</v>
       </c>
       <c r="B746" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B747" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
@@ -6807,7 +6822,7 @@
         <v>34</v>
       </c>
       <c r="B748" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
@@ -6828,31 +6843,31 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B751" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B752" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="754" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A754" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B754" s="4"/>
+      <c r="A754" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B754" s="5"/>
     </row>
     <row r="755" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A755" s="5" t="s">
+      <c r="A755" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B755" s="5"/>
+      <c r="B755" s="4"/>
     </row>
     <row r="756" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A756" s="3" t="s">
@@ -6864,10 +6879,10 @@
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B757" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.35">
@@ -6875,7 +6890,7 @@
         <v>4</v>
       </c>
       <c r="B758" t="s">
-        <v>67</v>
+        <v>267</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.35">
@@ -6883,7 +6898,7 @@
         <v>6</v>
       </c>
       <c r="B759" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.35">
@@ -6891,7 +6906,7 @@
         <v>8</v>
       </c>
       <c r="B760" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.35">
@@ -6947,7 +6962,7 @@
         <v>30</v>
       </c>
       <c r="B767" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.35">
@@ -6955,15 +6970,15 @@
         <v>32</v>
       </c>
       <c r="B768" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A769" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B769" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.35">
@@ -6971,7 +6986,7 @@
         <v>34</v>
       </c>
       <c r="B770" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.35">
@@ -6979,7 +6994,7 @@
         <v>36</v>
       </c>
       <c r="B771" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.35">
@@ -6991,16 +7006,16 @@
       </c>
     </row>
     <row r="774" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A774" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B774" s="4"/>
+      <c r="A774" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B774" s="5"/>
     </row>
     <row r="775" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A775" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B775" s="5"/>
+      <c r="A775" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B775" s="4"/>
     </row>
     <row r="776" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A776" s="3" t="s">
@@ -7012,10 +7027,10 @@
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A777" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B777" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.35">
@@ -7023,7 +7038,7 @@
         <v>4</v>
       </c>
       <c r="B778" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.35">
@@ -7031,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="B779" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.35">
@@ -7039,7 +7054,7 @@
         <v>8</v>
       </c>
       <c r="B780" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.35">
@@ -7047,7 +7062,7 @@
         <v>10</v>
       </c>
       <c r="B781" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.35">
@@ -7055,7 +7070,7 @@
         <v>12</v>
       </c>
       <c r="B782" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.35">
@@ -7063,7 +7078,7 @@
         <v>16</v>
       </c>
       <c r="B783" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.35">
@@ -7071,7 +7086,7 @@
         <v>18</v>
       </c>
       <c r="B784" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.35">
@@ -7079,7 +7094,7 @@
         <v>20</v>
       </c>
       <c r="B785" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.35">
@@ -7087,7 +7102,7 @@
         <v>22</v>
       </c>
       <c r="B786" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.35">
@@ -7095,7 +7110,7 @@
         <v>24</v>
       </c>
       <c r="B787" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.35">
@@ -7103,7 +7118,7 @@
         <v>30</v>
       </c>
       <c r="B788" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.35">
@@ -7111,15 +7126,15 @@
         <v>32</v>
       </c>
       <c r="B789" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A790" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B790" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.35">
@@ -7127,7 +7142,7 @@
         <v>34</v>
       </c>
       <c r="B791" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.35">
@@ -7135,7 +7150,7 @@
         <v>36</v>
       </c>
       <c r="B792" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.35">
@@ -7143,28 +7158,28 @@
         <v>38</v>
       </c>
       <c r="B793" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A794" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B794" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="796" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A796" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B796" s="4"/>
+      <c r="A796" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B796" s="5"/>
     </row>
     <row r="797" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A797" s="5" t="s">
+      <c r="A797" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B797" s="5"/>
+      <c r="B797" s="4"/>
     </row>
     <row r="798" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A798" s="3" t="s">
@@ -7176,10 +7191,10 @@
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A799" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B799" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.35">
@@ -7187,7 +7202,7 @@
         <v>4</v>
       </c>
       <c r="B800" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.35">
@@ -7195,7 +7210,7 @@
         <v>6</v>
       </c>
       <c r="B801" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.35">
@@ -7203,7 +7218,7 @@
         <v>8</v>
       </c>
       <c r="B802" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.35">
@@ -7211,7 +7226,7 @@
         <v>16</v>
       </c>
       <c r="B803" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.35">
@@ -7219,7 +7234,7 @@
         <v>18</v>
       </c>
       <c r="B804" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.35">
@@ -7227,7 +7242,7 @@
         <v>20</v>
       </c>
       <c r="B805" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.35">
@@ -7235,7 +7250,7 @@
         <v>22</v>
       </c>
       <c r="B806" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.35">
@@ -7243,7 +7258,7 @@
         <v>24</v>
       </c>
       <c r="B807" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.35">
@@ -7251,7 +7266,7 @@
         <v>26</v>
       </c>
       <c r="B808" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.35">
@@ -7259,7 +7274,7 @@
         <v>28</v>
       </c>
       <c r="B809" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.35">
@@ -7267,15 +7282,15 @@
         <v>30</v>
       </c>
       <c r="B810" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A811" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B811" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.35">
@@ -7283,15 +7298,15 @@
         <v>32</v>
       </c>
       <c r="B812" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A813" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B813" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.35">
@@ -7299,7 +7314,7 @@
         <v>34</v>
       </c>
       <c r="B814" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.35">
@@ -7307,20 +7322,20 @@
         <v>36</v>
       </c>
       <c r="B815" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="817" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A817" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B817" s="4"/>
+      <c r="A817" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B817" s="5"/>
     </row>
     <row r="818" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A818" s="5" t="s">
+      <c r="A818" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B818" s="5"/>
+      <c r="B818" s="4"/>
     </row>
     <row r="819" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A819" s="3" t="s">
@@ -7332,10 +7347,10 @@
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A820" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B820" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.35">
@@ -7343,7 +7358,7 @@
         <v>4</v>
       </c>
       <c r="B821" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.35">
@@ -7351,7 +7366,7 @@
         <v>6</v>
       </c>
       <c r="B822" t="s">
-        <v>110</v>
+        <v>269</v>
       </c>
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.35">
@@ -7359,7 +7374,7 @@
         <v>8</v>
       </c>
       <c r="B823" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.35">
@@ -7367,7 +7382,7 @@
         <v>12</v>
       </c>
       <c r="B824" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.35">
@@ -7375,7 +7390,7 @@
         <v>16</v>
       </c>
       <c r="B825" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.35">
@@ -7383,7 +7398,7 @@
         <v>18</v>
       </c>
       <c r="B826" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.35">
@@ -7391,7 +7406,7 @@
         <v>20</v>
       </c>
       <c r="B827" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.35">
@@ -7399,7 +7414,7 @@
         <v>22</v>
       </c>
       <c r="B828" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.35">
@@ -7407,7 +7422,7 @@
         <v>24</v>
       </c>
       <c r="B829" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.35">
@@ -7415,7 +7430,7 @@
         <v>26</v>
       </c>
       <c r="B830" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.35">
@@ -7423,7 +7438,7 @@
         <v>28</v>
       </c>
       <c r="B831" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.35">
@@ -7431,7 +7446,7 @@
         <v>30</v>
       </c>
       <c r="B832" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.35">
@@ -7439,15 +7454,15 @@
         <v>32</v>
       </c>
       <c r="B833" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A834" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B834" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.35">
@@ -7455,7 +7470,7 @@
         <v>34</v>
       </c>
       <c r="B835" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.35">
@@ -7463,7 +7478,7 @@
         <v>36</v>
       </c>
       <c r="B836" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.35">
@@ -7471,36 +7486,36 @@
         <v>38</v>
       </c>
       <c r="B837" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A838" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B838" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A839" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B839" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="841" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A841" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B841" s="4"/>
+      <c r="A841" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B841" s="5"/>
     </row>
     <row r="842" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A842" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B842" s="5"/>
+      <c r="A842" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B842" s="4"/>
     </row>
     <row r="843" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A843" s="3" t="s">
@@ -7512,10 +7527,10 @@
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A844" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B844" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.35">
@@ -7523,7 +7538,7 @@
         <v>4</v>
       </c>
       <c r="B845" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.35">
@@ -7531,7 +7546,7 @@
         <v>6</v>
       </c>
       <c r="B846" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.35">
@@ -7539,7 +7554,7 @@
         <v>8</v>
       </c>
       <c r="B847" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.35">
@@ -7547,7 +7562,7 @@
         <v>10</v>
       </c>
       <c r="B848" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.35">
@@ -7555,7 +7570,7 @@
         <v>12</v>
       </c>
       <c r="B849" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.35">
@@ -7563,7 +7578,7 @@
         <v>16</v>
       </c>
       <c r="B850" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.35">
@@ -7571,7 +7586,7 @@
         <v>18</v>
       </c>
       <c r="B851" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.35">
@@ -7579,7 +7594,7 @@
         <v>20</v>
       </c>
       <c r="B852" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.35">
@@ -7587,7 +7602,7 @@
         <v>22</v>
       </c>
       <c r="B853" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.35">
@@ -7595,7 +7610,7 @@
         <v>24</v>
       </c>
       <c r="B854" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.35">
@@ -7603,7 +7618,7 @@
         <v>26</v>
       </c>
       <c r="B855" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.35">
@@ -7611,7 +7626,7 @@
         <v>30</v>
       </c>
       <c r="B856" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.35">
@@ -7619,15 +7634,15 @@
         <v>32</v>
       </c>
       <c r="B857" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A858" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B858" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.35">
@@ -7635,7 +7650,7 @@
         <v>34</v>
       </c>
       <c r="B859" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.35">
@@ -7643,20 +7658,20 @@
         <v>36</v>
       </c>
       <c r="B860" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="862" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A862" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B862" s="4"/>
+      <c r="A862" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B862" s="5"/>
     </row>
     <row r="863" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A863" s="5" t="s">
+      <c r="A863" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B863" s="5"/>
+      <c r="B863" s="4"/>
     </row>
     <row r="864" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A864" s="3" t="s">
@@ -7668,10 +7683,10 @@
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A865" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B865" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.35">
@@ -7679,7 +7694,7 @@
         <v>4</v>
       </c>
       <c r="B866" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.35">
@@ -7695,7 +7710,7 @@
         <v>8</v>
       </c>
       <c r="B868" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.35">
@@ -7703,7 +7718,7 @@
         <v>10</v>
       </c>
       <c r="B869" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.35">
@@ -7711,7 +7726,7 @@
         <v>12</v>
       </c>
       <c r="B870" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.35">
@@ -7719,7 +7734,7 @@
         <v>16</v>
       </c>
       <c r="B871" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.35">
@@ -7727,7 +7742,7 @@
         <v>18</v>
       </c>
       <c r="B872" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.35">
@@ -7775,7 +7790,7 @@
         <v>30</v>
       </c>
       <c r="B878" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.35">
@@ -7783,15 +7798,15 @@
         <v>32</v>
       </c>
       <c r="B879" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A880" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B880" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.35">
@@ -7799,36 +7814,36 @@
         <v>34</v>
       </c>
       <c r="B881" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A882" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B882" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A883" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B883" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="885" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A885" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B885" s="4"/>
+      <c r="A885" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B885" s="5"/>
     </row>
     <row r="886" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A886" s="5" t="s">
+      <c r="A886" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B886" s="5"/>
+      <c r="B886" s="4"/>
     </row>
     <row r="887" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A887" s="3" t="s">
@@ -7840,7 +7855,7 @@
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A888" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B888" t="s">
         <v>33</v>
@@ -7859,7 +7874,7 @@
         <v>6</v>
       </c>
       <c r="B890" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.35">
@@ -7875,7 +7890,7 @@
         <v>10</v>
       </c>
       <c r="B892" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.35">
@@ -7891,7 +7906,7 @@
         <v>16</v>
       </c>
       <c r="B894" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.35">
@@ -7915,7 +7930,7 @@
         <v>22</v>
       </c>
       <c r="B897" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.35">
@@ -7952,7 +7967,7 @@
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A902" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B902" t="s">
         <v>19</v>
@@ -7963,7 +7978,7 @@
         <v>34</v>
       </c>
       <c r="B903" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.35">
@@ -7975,16 +7990,16 @@
       </c>
     </row>
     <row r="906" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A906" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B906" s="4"/>
+      <c r="A906" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B906" s="5"/>
     </row>
     <row r="907" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A907" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B907" s="5"/>
+      <c r="A907" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B907" s="4"/>
     </row>
     <row r="908" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A908" s="3" t="s">
@@ -7996,10 +8011,10 @@
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A909" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B909" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.35">
@@ -8007,7 +8022,7 @@
         <v>4</v>
       </c>
       <c r="B910" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.35">
@@ -8015,7 +8030,7 @@
         <v>6</v>
       </c>
       <c r="B911" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.35">
@@ -8023,7 +8038,7 @@
         <v>8</v>
       </c>
       <c r="B912" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.35">
@@ -8039,7 +8054,7 @@
         <v>16</v>
       </c>
       <c r="B914" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.35">
@@ -8047,7 +8062,7 @@
         <v>18</v>
       </c>
       <c r="B915" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.35">
@@ -8055,7 +8070,7 @@
         <v>20</v>
       </c>
       <c r="B916" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.35">
@@ -8063,7 +8078,7 @@
         <v>22</v>
       </c>
       <c r="B917" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.35">
@@ -8071,7 +8086,7 @@
         <v>24</v>
       </c>
       <c r="B918" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.35">
@@ -8079,15 +8094,15 @@
         <v>30</v>
       </c>
       <c r="B919" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A920" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B920" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.35">
@@ -8100,10 +8115,10 @@
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A922" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B922" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.35">
@@ -8111,36 +8126,36 @@
         <v>34</v>
       </c>
       <c r="B923" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A924" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B924" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A925" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B925" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="927" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A927" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B927" s="4"/>
+      <c r="A927" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B927" s="5"/>
     </row>
     <row r="928" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A928" s="5" t="s">
+      <c r="A928" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B928" s="5"/>
+      <c r="B928" s="4"/>
     </row>
     <row r="929" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A929" s="3" t="s">
@@ -8152,10 +8167,10 @@
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A930" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B930" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.35">
@@ -8163,7 +8178,7 @@
         <v>4</v>
       </c>
       <c r="B931" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.35">
@@ -8171,7 +8186,7 @@
         <v>6</v>
       </c>
       <c r="B932" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.35">
@@ -8179,7 +8194,7 @@
         <v>8</v>
       </c>
       <c r="B933" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.35">
@@ -8187,7 +8202,7 @@
         <v>10</v>
       </c>
       <c r="B934" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.35">
@@ -8195,7 +8210,7 @@
         <v>16</v>
       </c>
       <c r="B935" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.35">
@@ -8203,7 +8218,7 @@
         <v>18</v>
       </c>
       <c r="B936" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.35">
@@ -8211,7 +8226,7 @@
         <v>20</v>
       </c>
       <c r="B937" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.35">
@@ -8219,7 +8234,7 @@
         <v>22</v>
       </c>
       <c r="B938" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.35">
@@ -8227,7 +8242,7 @@
         <v>24</v>
       </c>
       <c r="B939" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.35">
@@ -8235,7 +8250,7 @@
         <v>26</v>
       </c>
       <c r="B940" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.35">
@@ -8243,7 +8258,7 @@
         <v>28</v>
       </c>
       <c r="B941" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.35">
@@ -8251,7 +8266,7 @@
         <v>30</v>
       </c>
       <c r="B942" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.35">
@@ -8259,15 +8274,15 @@
         <v>32</v>
       </c>
       <c r="B943" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A944" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B944" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.35">
@@ -8275,7 +8290,7 @@
         <v>34</v>
       </c>
       <c r="B945" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.35">
@@ -8283,36 +8298,36 @@
         <v>36</v>
       </c>
       <c r="B946" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A947" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B947" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A948" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B948" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="950" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A950" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B950" s="4"/>
+      <c r="A950" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B950" s="5"/>
     </row>
     <row r="951" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A951" s="5" t="s">
+      <c r="A951" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B951" s="5"/>
+      <c r="B951" s="4"/>
     </row>
     <row r="952" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A952" s="3" t="s">
@@ -8327,7 +8342,7 @@
         <v>4</v>
       </c>
       <c r="B953" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.35">
@@ -8335,7 +8350,7 @@
         <v>6</v>
       </c>
       <c r="B954" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.35">
@@ -8343,7 +8358,7 @@
         <v>8</v>
       </c>
       <c r="B955" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.35">
@@ -8351,7 +8366,7 @@
         <v>12</v>
       </c>
       <c r="B956" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.35">
@@ -8359,7 +8374,7 @@
         <v>14</v>
       </c>
       <c r="B957" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.35">
@@ -8367,7 +8382,7 @@
         <v>16</v>
       </c>
       <c r="B958" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.35">
@@ -8375,7 +8390,7 @@
         <v>18</v>
       </c>
       <c r="B959" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.35">
@@ -8383,7 +8398,7 @@
         <v>20</v>
       </c>
       <c r="B960" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.35">
@@ -8391,7 +8406,7 @@
         <v>22</v>
       </c>
       <c r="B961" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.35">
@@ -8399,7 +8414,7 @@
         <v>24</v>
       </c>
       <c r="B962" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.35">
@@ -8407,7 +8422,7 @@
         <v>26</v>
       </c>
       <c r="B963" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.35">
@@ -8415,7 +8430,7 @@
         <v>28</v>
       </c>
       <c r="B964" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.35">
@@ -8423,7 +8438,7 @@
         <v>30</v>
       </c>
       <c r="B965" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.35">
@@ -8431,15 +8446,15 @@
         <v>32</v>
       </c>
       <c r="B966" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A967" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B967" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.35">
@@ -8447,7 +8462,7 @@
         <v>34</v>
       </c>
       <c r="B968" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.35">
@@ -8455,36 +8470,36 @@
         <v>38</v>
       </c>
       <c r="B969" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A970" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B970" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A971" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B971" t="s">
-        <v>177</v>
+        <v>272</v>
       </c>
     </row>
     <row r="973" spans="1:2" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A973" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B973" s="4"/>
+      <c r="A973" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B973" s="5"/>
     </row>
     <row r="974" spans="1:2" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A974" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B974" s="5"/>
+      <c r="A974" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B974" s="4"/>
     </row>
     <row r="975" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A975" s="3" t="s">
@@ -8496,10 +8511,10 @@
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A976" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B976" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.35">
@@ -8507,7 +8522,7 @@
         <v>4</v>
       </c>
       <c r="B977" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.35">
@@ -8515,7 +8530,7 @@
         <v>8</v>
       </c>
       <c r="B978" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.35">
@@ -8523,7 +8538,7 @@
         <v>16</v>
       </c>
       <c r="B979" t="s">
-        <v>122</v>
+        <v>267</v>
       </c>
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.35">
@@ -8531,7 +8546,7 @@
         <v>18</v>
       </c>
       <c r="B980" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.35">
@@ -8539,7 +8554,7 @@
         <v>20</v>
       </c>
       <c r="B981" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.35">
@@ -8547,7 +8562,7 @@
         <v>22</v>
       </c>
       <c r="B982" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.35">
@@ -8555,7 +8570,7 @@
         <v>24</v>
       </c>
       <c r="B983" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.35">
@@ -8563,7 +8578,7 @@
         <v>26</v>
       </c>
       <c r="B984" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.35">
@@ -8571,7 +8586,7 @@
         <v>28</v>
       </c>
       <c r="B985" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.35">
@@ -8579,7 +8594,7 @@
         <v>30</v>
       </c>
       <c r="B986" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="987" spans="1:2" x14ac:dyDescent="0.35">
@@ -8587,15 +8602,15 @@
         <v>32</v>
       </c>
       <c r="B987" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="988" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A988" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B988" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.35">
@@ -8603,7 +8618,7 @@
         <v>34</v>
       </c>
       <c r="B989" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="990" spans="1:2" x14ac:dyDescent="0.35">
@@ -8611,101 +8626,101 @@
         <v>36</v>
       </c>
       <c r="B990" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="90">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="A161:B161"/>
+    <mergeCell ref="A184:B184"/>
+    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="A207:B207"/>
+    <mergeCell ref="A208:B208"/>
+    <mergeCell ref="A229:B229"/>
+    <mergeCell ref="A230:B230"/>
+    <mergeCell ref="A251:B251"/>
+    <mergeCell ref="A252:B252"/>
+    <mergeCell ref="A271:B271"/>
+    <mergeCell ref="A272:B272"/>
+    <mergeCell ref="A293:B293"/>
+    <mergeCell ref="A294:B294"/>
+    <mergeCell ref="A314:B314"/>
+    <mergeCell ref="A315:B315"/>
+    <mergeCell ref="A343:B343"/>
+    <mergeCell ref="A344:B344"/>
+    <mergeCell ref="A364:B364"/>
+    <mergeCell ref="A365:B365"/>
+    <mergeCell ref="A383:B383"/>
+    <mergeCell ref="A384:B384"/>
+    <mergeCell ref="A405:B405"/>
+    <mergeCell ref="A406:B406"/>
+    <mergeCell ref="A429:B429"/>
+    <mergeCell ref="A430:B430"/>
+    <mergeCell ref="A450:B450"/>
+    <mergeCell ref="A451:B451"/>
+    <mergeCell ref="A470:B470"/>
+    <mergeCell ref="A471:B471"/>
+    <mergeCell ref="A489:B489"/>
+    <mergeCell ref="A490:B490"/>
+    <mergeCell ref="A509:B509"/>
+    <mergeCell ref="A510:B510"/>
+    <mergeCell ref="A529:B529"/>
+    <mergeCell ref="A530:B530"/>
+    <mergeCell ref="A551:B551"/>
+    <mergeCell ref="A552:B552"/>
+    <mergeCell ref="A574:B574"/>
+    <mergeCell ref="A575:B575"/>
+    <mergeCell ref="A592:B592"/>
+    <mergeCell ref="A593:B593"/>
+    <mergeCell ref="A614:B614"/>
+    <mergeCell ref="A615:B615"/>
+    <mergeCell ref="A634:B634"/>
+    <mergeCell ref="A635:B635"/>
+    <mergeCell ref="A657:B657"/>
+    <mergeCell ref="A658:B658"/>
+    <mergeCell ref="A683:B683"/>
+    <mergeCell ref="A684:B684"/>
+    <mergeCell ref="A707:B707"/>
+    <mergeCell ref="A708:B708"/>
+    <mergeCell ref="A729:B729"/>
+    <mergeCell ref="A730:B730"/>
+    <mergeCell ref="A754:B754"/>
+    <mergeCell ref="A755:B755"/>
+    <mergeCell ref="A774:B774"/>
+    <mergeCell ref="A775:B775"/>
+    <mergeCell ref="A796:B796"/>
+    <mergeCell ref="A797:B797"/>
+    <mergeCell ref="A817:B817"/>
+    <mergeCell ref="A818:B818"/>
+    <mergeCell ref="A841:B841"/>
+    <mergeCell ref="A842:B842"/>
+    <mergeCell ref="A862:B862"/>
+    <mergeCell ref="A863:B863"/>
+    <mergeCell ref="A885:B885"/>
+    <mergeCell ref="A886:B886"/>
+    <mergeCell ref="A906:B906"/>
+    <mergeCell ref="A907:B907"/>
+    <mergeCell ref="A927:B927"/>
     <mergeCell ref="A928:B928"/>
     <mergeCell ref="A950:B950"/>
     <mergeCell ref="A951:B951"/>
     <mergeCell ref="A973:B973"/>
     <mergeCell ref="A974:B974"/>
-    <mergeCell ref="A885:B885"/>
-    <mergeCell ref="A886:B886"/>
-    <mergeCell ref="A906:B906"/>
-    <mergeCell ref="A907:B907"/>
-    <mergeCell ref="A927:B927"/>
-    <mergeCell ref="A818:B818"/>
-    <mergeCell ref="A841:B841"/>
-    <mergeCell ref="A842:B842"/>
-    <mergeCell ref="A862:B862"/>
-    <mergeCell ref="A863:B863"/>
-    <mergeCell ref="A774:B774"/>
-    <mergeCell ref="A775:B775"/>
-    <mergeCell ref="A796:B796"/>
-    <mergeCell ref="A797:B797"/>
-    <mergeCell ref="A817:B817"/>
-    <mergeCell ref="A708:B708"/>
-    <mergeCell ref="A729:B729"/>
-    <mergeCell ref="A730:B730"/>
-    <mergeCell ref="A754:B754"/>
-    <mergeCell ref="A755:B755"/>
-    <mergeCell ref="A657:B657"/>
-    <mergeCell ref="A658:B658"/>
-    <mergeCell ref="A683:B683"/>
-    <mergeCell ref="A684:B684"/>
-    <mergeCell ref="A707:B707"/>
-    <mergeCell ref="A593:B593"/>
-    <mergeCell ref="A614:B614"/>
-    <mergeCell ref="A615:B615"/>
-    <mergeCell ref="A634:B634"/>
-    <mergeCell ref="A635:B635"/>
-    <mergeCell ref="A551:B551"/>
-    <mergeCell ref="A552:B552"/>
-    <mergeCell ref="A574:B574"/>
-    <mergeCell ref="A575:B575"/>
-    <mergeCell ref="A592:B592"/>
-    <mergeCell ref="A490:B490"/>
-    <mergeCell ref="A509:B509"/>
-    <mergeCell ref="A510:B510"/>
-    <mergeCell ref="A529:B529"/>
-    <mergeCell ref="A530:B530"/>
-    <mergeCell ref="A450:B450"/>
-    <mergeCell ref="A451:B451"/>
-    <mergeCell ref="A470:B470"/>
-    <mergeCell ref="A471:B471"/>
-    <mergeCell ref="A489:B489"/>
-    <mergeCell ref="A384:B384"/>
-    <mergeCell ref="A405:B405"/>
-    <mergeCell ref="A406:B406"/>
-    <mergeCell ref="A429:B429"/>
-    <mergeCell ref="A430:B430"/>
-    <mergeCell ref="A343:B343"/>
-    <mergeCell ref="A344:B344"/>
-    <mergeCell ref="A364:B364"/>
-    <mergeCell ref="A365:B365"/>
-    <mergeCell ref="A383:B383"/>
-    <mergeCell ref="A272:B272"/>
-    <mergeCell ref="A293:B293"/>
-    <mergeCell ref="A294:B294"/>
-    <mergeCell ref="A314:B314"/>
-    <mergeCell ref="A315:B315"/>
-    <mergeCell ref="A229:B229"/>
-    <mergeCell ref="A230:B230"/>
-    <mergeCell ref="A251:B251"/>
-    <mergeCell ref="A252:B252"/>
-    <mergeCell ref="A271:B271"/>
-    <mergeCell ref="A161:B161"/>
-    <mergeCell ref="A184:B184"/>
-    <mergeCell ref="A185:B185"/>
-    <mergeCell ref="A207:B207"/>
-    <mergeCell ref="A208:B208"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="A160:B160"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A47:B47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -8714,7 +8729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -8723,10 +8738,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -8771,7 +8786,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -8779,7 +8794,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -8843,7 +8858,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>269</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -8851,7 +8866,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>7</v>
@@ -8859,7 +8874,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>7</v>
@@ -8867,7 +8882,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>7</v>
@@ -8875,7 +8890,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>7</v>
@@ -8883,7 +8898,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>7</v>
@@ -8891,7 +8906,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B22">
         <v>7</v>
@@ -8899,7 +8914,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="B23">
         <v>7</v>
@@ -8907,7 +8922,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>7</v>
@@ -8915,7 +8930,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>201</v>
+        <v>46</v>
       </c>
       <c r="B25">
         <v>7</v>
@@ -8923,7 +8938,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B26">
         <v>7</v>
@@ -8931,7 +8946,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="B27">
         <v>7</v>
@@ -8939,7 +8954,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B28">
         <v>7</v>
@@ -8947,7 +8962,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -8955,7 +8970,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B30">
         <v>7</v>
@@ -8963,7 +8978,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B31">
         <v>7</v>
@@ -8971,7 +8986,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32">
         <v>7</v>
@@ -8979,7 +8994,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33">
         <v>7</v>
@@ -8987,7 +9002,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B34">
         <v>7</v>
@@ -8995,7 +9010,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>273</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -9003,7 +9018,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B36">
         <v>7</v>
@@ -9011,7 +9026,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B37">
         <v>7</v>
@@ -9019,7 +9034,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="B38">
         <v>7</v>
@@ -9027,7 +9042,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B39">
         <v>7</v>
@@ -9035,7 +9050,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="B40">
         <v>7</v>
@@ -9043,7 +9058,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B41">
         <v>7</v>
@@ -9051,7 +9066,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42">
         <v>7</v>
@@ -9059,7 +9074,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B43">
         <v>7</v>
@@ -9067,15 +9082,15 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="B45">
         <v>7</v>
@@ -9083,7 +9098,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B46">
         <v>7</v>
@@ -9091,7 +9106,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="B47">
         <v>7</v>
@@ -9099,7 +9114,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
       <c r="B48">
         <v>7</v>
@@ -9107,7 +9122,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B49">
         <v>7</v>
@@ -9115,7 +9130,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B50">
         <v>7</v>
@@ -9123,7 +9138,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="B51">
         <v>7</v>
@@ -9131,7 +9146,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="B52">
         <v>7</v>
@@ -9139,7 +9154,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>208</v>
+        <v>139</v>
       </c>
       <c r="B53">
         <v>7</v>
@@ -9147,7 +9162,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="B54">
         <v>7</v>
@@ -9155,7 +9170,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="B55">
         <v>7</v>
@@ -9163,7 +9178,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>207</v>
       </c>
       <c r="B56">
         <v>7</v>
@@ -9171,7 +9186,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="B57">
         <v>7</v>
@@ -9179,7 +9194,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B58">
         <v>7</v>
@@ -9187,7 +9202,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B59">
         <v>7</v>
@@ -9195,7 +9210,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B60">
         <v>7</v>
@@ -9203,7 +9218,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B61">
         <v>7</v>
@@ -9211,7 +9226,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="B62">
         <v>7</v>
@@ -9219,7 +9234,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="B63">
         <v>7</v>
@@ -9227,7 +9242,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B64">
         <v>7</v>
@@ -9235,7 +9250,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="B65">
         <v>7</v>
@@ -9243,7 +9258,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="B66">
         <v>7</v>
@@ -9251,7 +9266,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B67">
         <v>7</v>
@@ -9259,7 +9274,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B68">
         <v>7</v>
@@ -9267,7 +9282,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="B69">
         <v>7</v>
@@ -9275,7 +9290,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B70">
         <v>7</v>
@@ -9291,7 +9306,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="B72">
         <v>7</v>
@@ -9299,7 +9314,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="B73">
         <v>7</v>
@@ -9307,7 +9322,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B74">
         <v>7</v>
@@ -9315,7 +9330,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>171</v>
       </c>
       <c r="B75">
         <v>7</v>
@@ -9323,7 +9338,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="B76">
         <v>7</v>
@@ -9331,15 +9346,15 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>224</v>
+        <v>93</v>
       </c>
       <c r="B77">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>225</v>
+        <v>94</v>
       </c>
       <c r="B78">
         <v>7</v>
@@ -9347,15 +9362,15 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B79">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>223</v>
       </c>
       <c r="B80">
         <v>7</v>
@@ -9363,7 +9378,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B81">
         <v>7</v>
@@ -9371,7 +9386,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B82">
         <v>7</v>
@@ -9379,7 +9394,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>97</v>
+        <v>224</v>
       </c>
       <c r="B83">
         <v>7</v>
@@ -9387,7 +9402,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B84">
         <v>7</v>
@@ -9395,7 +9410,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B85">
         <v>7</v>
@@ -9403,7 +9418,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="B86">
         <v>7</v>
@@ -9411,15 +9426,15 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>104</v>
+        <v>213</v>
       </c>
       <c r="B87">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>175</v>
+        <v>96</v>
       </c>
       <c r="B88">
         <v>7</v>
@@ -9427,7 +9442,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>211</v>
+        <v>95</v>
       </c>
       <c r="B89">
         <v>7</v>
@@ -9435,7 +9450,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B90">
         <v>7</v>
@@ -9443,23 +9458,23 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B91">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B92">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="B93">
         <v>7</v>
@@ -9467,15 +9482,15 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>210</v>
       </c>
       <c r="B94">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B95">
         <v>7</v>
@@ -9483,7 +9498,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="B96">
         <v>7</v>
@@ -9491,31 +9506,31 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="B97">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B98">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B99">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B100">
         <v>7</v>
@@ -9523,7 +9538,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="B101">
         <v>7</v>
@@ -9531,7 +9546,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="B102">
         <v>7</v>
@@ -9539,7 +9554,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B103">
         <v>7</v>
@@ -9547,7 +9562,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B104">
         <v>7</v>
@@ -9555,15 +9570,15 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B105">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="B106">
         <v>7</v>
@@ -9571,7 +9586,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B107">
         <v>7</v>
@@ -9579,7 +9594,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B108">
         <v>7</v>
@@ -9587,7 +9602,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B109">
         <v>7</v>
@@ -9595,7 +9610,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
       <c r="B110">
         <v>7</v>
@@ -9603,23 +9618,23 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="B111">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="B112">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B113">
         <v>7</v>
@@ -9627,7 +9642,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="B114">
         <v>7</v>
@@ -9635,7 +9650,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="B115">
         <v>7</v>
@@ -9643,7 +9658,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="B116">
         <v>7</v>
@@ -9651,7 +9666,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B117">
         <v>6</v>
@@ -9659,7 +9674,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="B118">
         <v>6</v>
@@ -9667,7 +9682,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="B119">
         <v>6</v>
@@ -9675,7 +9690,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B120">
         <v>6</v>
@@ -9683,7 +9698,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="B121">
         <v>6</v>
@@ -9691,7 +9706,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B122">
         <v>6</v>
@@ -9699,7 +9714,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>232</v>
+        <v>116</v>
       </c>
       <c r="B123">
         <v>6</v>
@@ -9707,7 +9722,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B124">
         <v>6</v>
@@ -9715,7 +9730,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="B125">
         <v>6</v>
@@ -9723,7 +9738,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B126">
         <v>6</v>
@@ -9731,7 +9746,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B127">
         <v>6</v>
@@ -9739,7 +9754,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B128">
         <v>6</v>
@@ -9747,7 +9762,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B129">
         <v>6</v>
@@ -9755,7 +9770,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="B130">
         <v>6</v>
@@ -9771,7 +9786,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="B132">
         <v>6</v>
@@ -9795,7 +9810,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B135">
         <v>6</v>
@@ -9803,7 +9818,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B136">
         <v>6</v>
@@ -9811,7 +9826,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B137">
         <v>6</v>
@@ -9819,7 +9834,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B138">
         <v>6</v>
@@ -9827,10 +9842,26 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B139">
         <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>145</v>
+      </c>
+      <c r="B140">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>267</v>
+      </c>
+      <c r="B141">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
